--- a/STOK RANK/Rank Dealer/RANK HPN.xlsx
+++ b/STOK RANK/Rank Dealer/RANK HPN.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\DASHBOARD RANK STOK\data\Rank Dealer\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00BE5194-F27C-47F9-B9CF-F66FD09872B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F5E8660-BDA1-406B-8A1B-33278FF24E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{B751393D-4C32-4D4C-AA97-AA7CC129AC75}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="630" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="247">
   <si>
     <t>Sum of Qty</t>
   </si>
@@ -210,15 +210,9 @@
     <t>42711K0WN01</t>
   </si>
   <si>
-    <t>42711K59A72</t>
-  </si>
-  <si>
     <t>44711K0WN01</t>
   </si>
   <si>
-    <t>44711K2SN01</t>
-  </si>
-  <si>
     <t>64310K1AN00ZA</t>
   </si>
   <si>
@@ -237,9 +231,6 @@
     <t>64202K2FN00YF</t>
   </si>
   <si>
-    <t>12251GGC901</t>
-  </si>
-  <si>
     <t>23100KVBBA0</t>
   </si>
   <si>
@@ -321,12 +312,6 @@
     <t>87100LXBLUL</t>
   </si>
   <si>
-    <t>08F88K1ZG00</t>
-  </si>
-  <si>
-    <t>AHTS0301052</t>
-  </si>
-  <si>
     <t>Sum 6 Bulan</t>
   </si>
   <si>
@@ -375,9 +360,6 @@
     <t>22105KWN900</t>
   </si>
   <si>
-    <t>22535K2FN00</t>
-  </si>
-  <si>
     <t>35148K78N10</t>
   </si>
   <si>
@@ -498,9 +480,6 @@
     <t>17210K97N00</t>
   </si>
   <si>
-    <t>51410K0JN01</t>
-  </si>
-  <si>
     <t>19216KVB900</t>
   </si>
   <si>
@@ -522,9 +501,6 @@
     <t>91201K44V01</t>
   </si>
   <si>
-    <t>06455KR3404</t>
-  </si>
-  <si>
     <t>22102KWN900</t>
   </si>
   <si>
@@ -534,9 +510,6 @@
     <t>81130K2FN80ZL</t>
   </si>
   <si>
-    <t>17210KVB930</t>
-  </si>
-  <si>
     <t>12100K1ZT00</t>
   </si>
   <si>
@@ -549,36 +522,18 @@
     <t>64421K0JN00ZE</t>
   </si>
   <si>
-    <t>34901K81N01</t>
-  </si>
-  <si>
     <t>81141K93N00ZJ</t>
   </si>
   <si>
-    <t>12391K66V01</t>
-  </si>
-  <si>
     <t>22102K1ZN20</t>
   </si>
   <si>
-    <t>35010K1AN00</t>
-  </si>
-  <si>
     <t>52400KVB931</t>
   </si>
   <si>
-    <t>16450K15921</t>
-  </si>
-  <si>
     <t>14401KYZ900</t>
   </si>
   <si>
-    <t>131A1K0JP00</t>
-  </si>
-  <si>
-    <t>16700K60B61</t>
-  </si>
-  <si>
     <t>06401KYE900</t>
   </si>
   <si>
@@ -588,9 +543,6 @@
     <t>64501K2SN00ZK</t>
   </si>
   <si>
-    <t>38502KWN901</t>
-  </si>
-  <si>
     <t>14520K94T01</t>
   </si>
   <si>
@@ -624,9 +576,6 @@
     <t>64201K93N00ZK</t>
   </si>
   <si>
-    <t>06401K56N11</t>
-  </si>
-  <si>
     <t>64305K81N00ZA</t>
   </si>
   <si>
@@ -636,9 +585,6 @@
     <t>17910K03N31</t>
   </si>
   <si>
-    <t>23205K93N00</t>
-  </si>
-  <si>
     <t>64360K2SN00ZA</t>
   </si>
   <si>
@@ -669,15 +615,9 @@
     <t>17210K93N00</t>
   </si>
   <si>
-    <t>16700K03H01</t>
-  </si>
-  <si>
     <t>131A3K0JP00</t>
   </si>
   <si>
-    <t>06401K45N01</t>
-  </si>
-  <si>
     <t>17910KVR600</t>
   </si>
   <si>
@@ -693,9 +633,6 @@
     <t>12251K1ZJ11</t>
   </si>
   <si>
-    <t>16400K16A41</t>
-  </si>
-  <si>
     <t>31500KWWA01</t>
   </si>
   <si>
@@ -711,73 +648,136 @@
     <t>87100LXWHTL</t>
   </si>
   <si>
-    <t>87100FSBEIM</t>
-  </si>
-  <si>
     <t>AHPS0104012</t>
   </si>
   <si>
-    <t>AHPS0106012</t>
-  </si>
-  <si>
-    <t>AHTS0101051</t>
-  </si>
-  <si>
-    <t>87100HFFABL</t>
-  </si>
-  <si>
-    <t>AHJK0201030</t>
-  </si>
-  <si>
-    <t>AHPS0206012</t>
-  </si>
-  <si>
-    <t>87100LXREDM</t>
-  </si>
-  <si>
-    <t>AHGK0010010</t>
-  </si>
-  <si>
-    <t>AHPS0204012</t>
-  </si>
-  <si>
     <t>AHPS0304012</t>
   </si>
   <si>
-    <t>AHTS0301050</t>
-  </si>
-  <si>
     <t>17200K1ZG00</t>
   </si>
   <si>
-    <t>87100FSSAGL</t>
-  </si>
-  <si>
-    <t>AHGK0010012</t>
-  </si>
-  <si>
-    <t>AHPS0103012</t>
-  </si>
-  <si>
     <t>AHPS0105012</t>
   </si>
   <si>
-    <t>AHPS0203012</t>
-  </si>
-  <si>
     <t>AHPS0205012</t>
   </si>
   <si>
-    <t>AHPS0303012</t>
-  </si>
-  <si>
-    <t>AHTP0003016</t>
-  </si>
-  <si>
-    <t>AHTS0201050</t>
-  </si>
-  <si>
-    <t>AHTS0301051</t>
+    <t>22102KZR600</t>
+  </si>
+  <si>
+    <t>9805657723</t>
+  </si>
+  <si>
+    <t>42711K2SN01</t>
+  </si>
+  <si>
+    <t>12100KFM900</t>
+  </si>
+  <si>
+    <t>64320K2SN00ZA</t>
+  </si>
+  <si>
+    <t>64431K1ZJ10ZS</t>
+  </si>
+  <si>
+    <t>13000K2FN00</t>
+  </si>
+  <si>
+    <t>33100K1ZN21</t>
+  </si>
+  <si>
+    <t>9410912000</t>
+  </si>
+  <si>
+    <t>64501K1ZJ10ZP</t>
+  </si>
+  <si>
+    <t>91109KVY901</t>
+  </si>
+  <si>
+    <t>131A2K0JP00</t>
+  </si>
+  <si>
+    <t>64420K2SN00ZA</t>
+  </si>
+  <si>
+    <t>22105KZLC00</t>
+  </si>
+  <si>
+    <t>81131K1ZJ10ZC</t>
+  </si>
+  <si>
+    <t>81145K59A70ZB</t>
+  </si>
+  <si>
+    <t>91009KVY961</t>
+  </si>
+  <si>
+    <t>31220K81N01</t>
+  </si>
+  <si>
+    <t>17211K18900</t>
+  </si>
+  <si>
+    <t>91211KN7671</t>
+  </si>
+  <si>
+    <t>64308K1AN00ZA</t>
+  </si>
+  <si>
+    <t>35340KWB601</t>
+  </si>
+  <si>
+    <t>31500KPH882</t>
+  </si>
+  <si>
+    <t>ACL70ML</t>
+  </si>
+  <si>
+    <t>64300K2FP00</t>
+  </si>
+  <si>
+    <t>87100LXREDL</t>
+  </si>
+  <si>
+    <t>64300K1AA00</t>
+  </si>
+  <si>
+    <t>HIC60ML</t>
+  </si>
+  <si>
+    <t>HPC480ML</t>
+  </si>
+  <si>
+    <t>08F88K1AA00</t>
+  </si>
+  <si>
+    <t>87100FSBEIL</t>
+  </si>
+  <si>
+    <t>AHK01001016</t>
+  </si>
+  <si>
+    <t>AHPS0005012</t>
+  </si>
+  <si>
+    <t>0800CK2FPKU</t>
+  </si>
+  <si>
+    <t>0800DK2FPKU</t>
+  </si>
+  <si>
+    <t>64300K1AL00</t>
+  </si>
+  <si>
+    <t>87100FSSAGXL</t>
+  </si>
+  <si>
+    <t>87100LXWHTXL</t>
+  </si>
+  <si>
+    <t>AHPS0201013</t>
   </si>
 </sst>
 </file>
@@ -864,8 +864,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C03BE401-9C1F-4F8C-A0F0-B1258C79C616}" name="rankparts" displayName="rankparts" ref="A1:F196" totalsRowShown="0">
-  <autoFilter ref="A1:F196" xr:uid="{C03BE401-9C1F-4F8C-A0F0-B1258C79C616}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C03BE401-9C1F-4F8C-A0F0-B1258C79C616}" name="rankparts" displayName="rankparts" ref="A1:F197" totalsRowShown="0">
+  <autoFilter ref="A1:F197" xr:uid="{C03BE401-9C1F-4F8C-A0F0-B1258C79C616}"/>
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{EC489C37-CEDC-4675-8D70-1D331AA94B51}" name="kode part" dataDxfId="3"/>
     <tableColumn id="2" xr3:uid="{36D6B850-0C62-4808-8CA4-A3ADDE283157}" name="Sum of Qty"/>
@@ -879,8 +879,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C03400FD-64EB-41AC-8C3F-E00487FB0DC0}" name="AVG6bulan" displayName="AVG6bulan" ref="A1:C238" totalsRowShown="0">
-  <autoFilter ref="A1:C238" xr:uid="{C03400FD-64EB-41AC-8C3F-E00487FB0DC0}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{C03400FD-64EB-41AC-8C3F-E00487FB0DC0}" name="AVG6bulan" displayName="AVG6bulan" ref="A1:C235" totalsRowShown="0">
+  <autoFilter ref="A1:C235" xr:uid="{C03400FD-64EB-41AC-8C3F-E00487FB0DC0}"/>
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{EA290633-F868-4318-B60E-FE8A74ECF04D}" name="kode part" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{53B0B34D-5627-4ECE-B3FA-95091F3CF241}" name="Sum 6 Bulan"/>
@@ -1207,7 +1207,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10CE7CC1-6D2C-42F4-9AE1-2E1B51ED5CAA}">
-  <dimension ref="A1:F196"/>
+  <dimension ref="A1:F197"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" style="3" bestFit="1" customWidth="1"/>
@@ -1219,7 +1219,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1239,19 +1239,19 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B2">
-        <v>468</v>
+        <v>402</v>
       </c>
       <c r="C2" s="1">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D2" s="1">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="E2" s="2">
-        <v>0.11923566878980919</v>
+        <v>0.10832659660468898</v>
       </c>
       <c r="F2" t="s">
         <v>5</v>
@@ -1259,19 +1259,19 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B3">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="C3" s="1">
-        <v>43.166666666666664</v>
+        <v>41</v>
       </c>
       <c r="D3" s="1">
-        <v>121.16666666666666</v>
+        <v>108</v>
       </c>
       <c r="E3" s="2">
-        <v>0.18522292993630615</v>
+        <v>0.17461600646725986</v>
       </c>
       <c r="F3" t="s">
         <v>5</v>
@@ -1282,16 +1282,16 @@
         <v>12</v>
       </c>
       <c r="B4">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="C4" s="1">
-        <v>38.333333333333336</v>
+        <v>35.333333333333336</v>
       </c>
       <c r="D4" s="1">
-        <v>159.5</v>
+        <v>143.33333333333334</v>
       </c>
       <c r="E4" s="2">
-        <v>0.24382165605095599</v>
+        <v>0.23174346537321525</v>
       </c>
       <c r="F4" t="s">
         <v>5</v>
@@ -1302,16 +1302,16 @@
         <v>7</v>
       </c>
       <c r="B5">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="C5" s="1">
-        <v>33.5</v>
+        <v>35.166666666666664</v>
       </c>
       <c r="D5" s="1">
-        <v>193</v>
+        <v>178.5</v>
       </c>
       <c r="E5" s="2">
-        <v>0.29503184713375863</v>
+        <v>0.28860145513338781</v>
       </c>
       <c r="F5" t="s">
         <v>5</v>
@@ -1322,16 +1322,16 @@
         <v>8</v>
       </c>
       <c r="B6">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C6" s="1">
-        <v>30.5</v>
+        <v>30.833333333333332</v>
       </c>
       <c r="D6" s="1">
-        <v>223.5</v>
+        <v>209.33333333333334</v>
       </c>
       <c r="E6" s="2">
-        <v>0.34165605095541479</v>
+        <v>0.3384532471032074</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
@@ -1339,19 +1339,19 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B7">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C7" s="1">
-        <v>23.166666666666668</v>
+        <v>21.333333333333332</v>
       </c>
       <c r="D7" s="1">
-        <v>246.66666666666666</v>
+        <v>230.66666666666669</v>
       </c>
       <c r="E7" s="2">
-        <v>0.37707006369426838</v>
+        <v>0.3729452977634069</v>
       </c>
       <c r="F7" t="s">
         <v>5</v>
@@ -1359,19 +1359,19 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B8">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C8" s="1">
-        <v>21.666666666666668</v>
+        <v>20.666666666666668</v>
       </c>
       <c r="D8" s="1">
-        <v>268.33333333333331</v>
+        <v>251.33333333333334</v>
       </c>
       <c r="E8" s="2">
-        <v>0.41019108280254868</v>
+        <v>0.40635947184047511</v>
       </c>
       <c r="F8" t="s">
         <v>5</v>
@@ -1379,19 +1379,19 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="B9">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="C9" s="1">
-        <v>18.5</v>
+        <v>20.333333333333332</v>
       </c>
       <c r="D9" s="1">
-        <v>286.83333333333331</v>
+        <v>271.66666666666669</v>
       </c>
       <c r="E9" s="2">
-        <v>0.43847133757961881</v>
+        <v>0.43923470762597777</v>
       </c>
       <c r="F9" t="s">
         <v>5</v>
@@ -1399,19 +1399,19 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B10">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C10" s="1">
-        <v>18.166666666666668</v>
+        <v>18</v>
       </c>
       <c r="D10" s="1">
-        <v>305</v>
+        <v>289.66666666666669</v>
       </c>
       <c r="E10" s="2">
-        <v>0.46624203821656157</v>
+        <v>0.46833737537052106</v>
       </c>
       <c r="F10" t="s">
         <v>5</v>
@@ -1419,19 +1419,19 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>102</v>
+        <v>16</v>
       </c>
       <c r="B11">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C11" s="1">
-        <v>16.833333333333332</v>
+        <v>17.833333333333332</v>
       </c>
       <c r="D11" s="1">
-        <v>321.83333333333331</v>
+        <v>307.5</v>
       </c>
       <c r="E11" s="2">
-        <v>0.49197452229299476</v>
+        <v>0.49717057396928155</v>
       </c>
       <c r="F11" t="s">
         <v>5</v>
@@ -1439,19 +1439,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B12">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C12" s="1">
-        <v>15.833333333333334</v>
+        <v>15.5</v>
       </c>
       <c r="D12" s="1">
-        <v>337.66666666666663</v>
+        <v>323</v>
       </c>
       <c r="E12" s="2">
-        <v>0.51617834394904571</v>
+        <v>0.52223120452708272</v>
       </c>
       <c r="F12" t="s">
         <v>5</v>
@@ -1459,19 +1459,19 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="B13">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C13" s="1">
-        <v>13.666666666666666</v>
+        <v>14</v>
       </c>
       <c r="D13" s="1">
-        <v>351.33333333333331</v>
+        <v>337</v>
       </c>
       <c r="E13" s="2">
-        <v>0.53707006369426868</v>
+        <v>0.54486661277283865</v>
       </c>
       <c r="F13" t="s">
         <v>5</v>
@@ -1479,19 +1479,19 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B14">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C14" s="1">
-        <v>13</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="D14" s="1">
-        <v>364.33333333333331</v>
+        <v>350.33333333333331</v>
       </c>
       <c r="E14" s="2">
-        <v>0.5569426751592369</v>
+        <v>0.56642414443546329</v>
       </c>
       <c r="F14" t="s">
         <v>5</v>
@@ -1499,19 +1499,19 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>11</v>
+        <v>97</v>
       </c>
       <c r="B15">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="C15" s="1">
-        <v>12.833333333333334</v>
+        <v>11.833333333333334</v>
       </c>
       <c r="D15" s="1">
-        <v>377.16666666666663</v>
+        <v>362.16666666666663</v>
       </c>
       <c r="E15" s="2">
-        <v>0.5765605095541414</v>
+        <v>0.5855564537860426</v>
       </c>
       <c r="F15" t="s">
         <v>5</v>
@@ -1519,19 +1519,19 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="B16">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C16" s="1">
-        <v>11.833333333333334</v>
+        <v>11.666666666666666</v>
       </c>
       <c r="D16" s="1">
-        <v>388.99999999999994</v>
+        <v>373.83333333333331</v>
       </c>
       <c r="E16" s="2">
-        <v>0.59464968152866371</v>
+        <v>0.60441929399083927</v>
       </c>
       <c r="F16" t="s">
         <v>5</v>
@@ -1539,19 +1539,19 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B17">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="C17" s="1">
-        <v>11.666666666666666</v>
+        <v>10.833333333333334</v>
       </c>
       <c r="D17" s="1">
-        <v>400.66666666666663</v>
+        <v>384.66666666666663</v>
       </c>
       <c r="E17" s="2">
-        <v>0.61248407643312242</v>
+        <v>0.62193478846672179</v>
       </c>
       <c r="F17" t="s">
         <v>5</v>
@@ -1559,19 +1559,19 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="B18">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="C18" s="1">
-        <v>11.166666666666666</v>
+        <v>9.6666666666666661</v>
       </c>
       <c r="D18" s="1">
-        <v>411.83333333333331</v>
+        <v>394.33333333333331</v>
       </c>
       <c r="E18" s="2">
-        <v>0.62955414012738997</v>
+        <v>0.63756399892212468</v>
       </c>
       <c r="F18" t="s">
         <v>5</v>
@@ -1579,19 +1579,19 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="B19">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C19" s="1">
-        <v>10.166666666666666</v>
+        <v>8.8333333333333339</v>
       </c>
       <c r="D19" s="1">
-        <v>422</v>
+        <v>403.16666666666663</v>
       </c>
       <c r="E19" s="2">
-        <v>0.64509554140127534</v>
+        <v>0.65184586364861352</v>
       </c>
       <c r="F19" t="s">
         <v>5</v>
@@ -1599,19 +1599,19 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="B20">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C20" s="1">
-        <v>10.166666666666666</v>
+        <v>8.6666666666666661</v>
       </c>
       <c r="D20" s="1">
-        <v>432.16666666666669</v>
+        <v>411.83333333333331</v>
       </c>
       <c r="E20" s="2">
-        <v>0.66063694267516082</v>
+        <v>0.66585825922931952</v>
       </c>
       <c r="F20" t="s">
         <v>5</v>
@@ -1619,19 +1619,19 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>104</v>
+        <v>27</v>
       </c>
       <c r="B21">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="C21" s="1">
-        <v>9.5</v>
+        <v>8.3333333333333339</v>
       </c>
       <c r="D21" s="1">
-        <v>441.66666666666669</v>
+        <v>420.16666666666663</v>
       </c>
       <c r="E21" s="2">
-        <v>0.67515923566879144</v>
+        <v>0.67933171651845992</v>
       </c>
       <c r="F21" t="s">
         <v>5</v>
@@ -1639,19 +1639,19 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B22">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C22" s="1">
-        <v>9.5</v>
+        <v>8.1666666666666661</v>
       </c>
       <c r="D22" s="1">
-        <v>451.16666666666669</v>
+        <v>428.33333333333331</v>
       </c>
       <c r="E22" s="2">
-        <v>0.68968152866242205</v>
+        <v>0.69253570466181757</v>
       </c>
       <c r="F22" t="s">
         <v>5</v>
@@ -1659,19 +1659,19 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="B23">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="C23" s="1">
-        <v>9.3333333333333339</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="D23" s="1">
-        <v>460.5</v>
+        <v>435.5</v>
       </c>
       <c r="E23" s="2">
-        <v>0.70394904458598895</v>
+        <v>0.70412287793047834</v>
       </c>
       <c r="F23" t="s">
         <v>5</v>
@@ -1679,19 +1679,19 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>9</v>
+        <v>99</v>
       </c>
       <c r="B24">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C24" s="1">
-        <v>9.1666666666666661</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="D24" s="1">
-        <v>469.66666666666669</v>
+        <v>442.16666666666669</v>
       </c>
       <c r="E24" s="2">
-        <v>0.71796178343949213</v>
+        <v>0.71490164376179077</v>
       </c>
       <c r="F24" t="s">
         <v>5</v>
@@ -1699,19 +1699,19 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="B25">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C25" s="1">
-        <v>7.166666666666667</v>
+        <v>6.333333333333333</v>
       </c>
       <c r="D25" s="1">
-        <v>476.83333333333337</v>
+        <v>448.5</v>
       </c>
       <c r="E25" s="2">
-        <v>0.72891719745223105</v>
+        <v>0.72514147130153739</v>
       </c>
       <c r="F25" t="s">
         <v>5</v>
@@ -1722,16 +1722,16 @@
         <v>17</v>
       </c>
       <c r="B26">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C26" s="1">
-        <v>6.5</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="D26" s="1">
-        <v>483.33333333333337</v>
+        <v>454.66666666666669</v>
       </c>
       <c r="E26" s="2">
-        <v>0.7388535031847151</v>
+        <v>0.73511182969550137</v>
       </c>
       <c r="F26" t="s">
         <v>5</v>
@@ -1739,19 +1739,19 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B27">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C27" s="1">
-        <v>6.333333333333333</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="D27" s="1">
-        <v>489.66666666666669</v>
+        <v>460.5</v>
       </c>
       <c r="E27" s="2">
-        <v>0.74853503184713555</v>
+        <v>0.74454324979789965</v>
       </c>
       <c r="F27" t="s">
         <v>5</v>
@@ -1759,19 +1759,19 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="B28">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C28" s="1">
-        <v>6.333333333333333</v>
+        <v>5.5</v>
       </c>
       <c r="D28" s="1">
-        <v>496</v>
+        <v>466</v>
       </c>
       <c r="E28" s="2">
-        <v>0.75821656050955588</v>
+        <v>0.75343573160873234</v>
       </c>
       <c r="F28" t="s">
         <v>5</v>
@@ -1779,19 +1779,19 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="B29">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C29" s="1">
-        <v>6</v>
+        <v>5.333333333333333</v>
       </c>
       <c r="D29" s="1">
-        <v>502</v>
+        <v>471.33333333333331</v>
       </c>
       <c r="E29" s="2">
-        <v>0.7673885350318489</v>
+        <v>0.76205874427378217</v>
       </c>
       <c r="F29" t="s">
         <v>5</v>
@@ -1799,19 +1799,19 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="B30">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C30" s="1">
-        <v>5.666666666666667</v>
+        <v>5.166666666666667</v>
       </c>
       <c r="D30" s="1">
-        <v>507.66666666666669</v>
+        <v>476.5</v>
       </c>
       <c r="E30" s="2">
-        <v>0.77605095541401459</v>
+        <v>0.77041228779304927</v>
       </c>
       <c r="F30" t="s">
         <v>5</v>
@@ -1819,19 +1819,19 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B31">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C31" s="1">
-        <v>5.166666666666667</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="D31" s="1">
-        <v>512.83333333333337</v>
+        <v>481.33333333333331</v>
       </c>
       <c r="E31" s="2">
-        <v>0.78394904458598913</v>
+        <v>0.77822689302075065</v>
       </c>
       <c r="F31" t="s">
         <v>5</v>
@@ -1839,19 +1839,19 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>18</v>
+        <v>102</v>
       </c>
       <c r="B32">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C32" s="1">
-        <v>5</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="D32" s="1">
-        <v>517.83333333333337</v>
+        <v>486.16666666666663</v>
       </c>
       <c r="E32" s="2">
-        <v>0.79159235668789996</v>
+        <v>0.78604149824845204</v>
       </c>
       <c r="F32" t="s">
         <v>5</v>
@@ -1859,19 +1859,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="B33">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C33" s="1">
-        <v>5</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="D33" s="1">
-        <v>522.83333333333337</v>
+        <v>490.83333333333331</v>
       </c>
       <c r="E33" s="2">
-        <v>0.79923566878981078</v>
+        <v>0.7935866343303708</v>
       </c>
       <c r="F33" t="s">
         <v>5</v>
@@ -1879,7 +1879,7 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="B34">
         <v>28</v>
@@ -1888,10 +1888,10 @@
         <v>4.666666666666667</v>
       </c>
       <c r="D34" s="1">
-        <v>527.5</v>
+        <v>495.5</v>
       </c>
       <c r="E34" s="2">
-        <v>0.80636942675159418</v>
+        <v>0.80113177041228945</v>
       </c>
       <c r="F34" t="s">
         <v>5</v>
@@ -1899,19 +1899,19 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B35">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C35" s="1">
-        <v>4.5</v>
+        <v>4.666666666666667</v>
       </c>
       <c r="D35" s="1">
-        <v>532</v>
+        <v>500.16666666666669</v>
       </c>
       <c r="E35" s="2">
-        <v>0.81324840764331396</v>
+        <v>0.80867690649420809</v>
       </c>
       <c r="F35" t="s">
         <v>5</v>
@@ -1919,19 +1919,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>76</v>
+        <v>18</v>
       </c>
       <c r="B36">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C36" s="1">
-        <v>4.5</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="D36" s="1">
-        <v>536.5</v>
+        <v>504.33333333333337</v>
       </c>
       <c r="E36" s="2">
-        <v>0.82012738853503375</v>
+        <v>0.81541363513877829</v>
       </c>
       <c r="F36" t="s">
         <v>5</v>
@@ -1939,19 +1939,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="B37">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C37" s="1">
-        <v>4.333333333333333</v>
+        <v>3.8333333333333335</v>
       </c>
       <c r="D37" s="1">
-        <v>540.83333333333337</v>
+        <v>508.16666666666669</v>
       </c>
       <c r="E37" s="2">
-        <v>0.82675159235668982</v>
+        <v>0.8216114254917829</v>
       </c>
       <c r="F37" t="s">
         <v>5</v>
@@ -1959,19 +1959,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B38">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C38" s="1">
-        <v>3.8333333333333335</v>
+        <v>3.6666666666666665</v>
       </c>
       <c r="D38" s="1">
-        <v>544.66666666666674</v>
+        <v>511.83333333333337</v>
       </c>
       <c r="E38" s="2">
-        <v>0.83261146496815486</v>
+        <v>0.82753974669900465</v>
       </c>
       <c r="F38" t="s">
         <v>5</v>
@@ -1979,19 +1979,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>109</v>
+        <v>21</v>
       </c>
       <c r="B39">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C39" s="1">
-        <v>3.8333333333333335</v>
+        <v>3.6666666666666665</v>
       </c>
       <c r="D39" s="1">
-        <v>548.50000000000011</v>
+        <v>515.5</v>
       </c>
       <c r="E39" s="2">
-        <v>0.83847133757962</v>
+        <v>0.83346806790622641</v>
       </c>
       <c r="F39" t="s">
         <v>5</v>
@@ -1999,19 +1999,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B40">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C40" s="1">
-        <v>3.6666666666666665</v>
+        <v>3.5</v>
       </c>
       <c r="D40" s="1">
-        <v>552.16666666666674</v>
+        <v>519</v>
       </c>
       <c r="E40" s="2">
-        <v>0.84407643312102121</v>
+        <v>0.83912691996766542</v>
       </c>
       <c r="F40" t="s">
         <v>5</v>
@@ -2019,7 +2019,7 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B41">
         <v>21</v>
@@ -2028,10 +2028,10 @@
         <v>3.5</v>
       </c>
       <c r="D41" s="1">
-        <v>555.66666666666674</v>
+        <v>522.5</v>
       </c>
       <c r="E41" s="2">
-        <v>0.84942675159235881</v>
+        <v>0.84478577202910432</v>
       </c>
       <c r="F41" t="s">
         <v>5</v>
@@ -2039,19 +2039,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B42">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C42" s="1">
-        <v>3.3333333333333335</v>
+        <v>3.5</v>
       </c>
       <c r="D42" s="1">
-        <v>559.00000000000011</v>
+        <v>526</v>
       </c>
       <c r="E42" s="2">
-        <v>0.85452229299363269</v>
+        <v>0.85044462409054333</v>
       </c>
       <c r="F42" t="s">
         <v>5</v>
@@ -2059,19 +2059,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="B43">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C43" s="1">
-        <v>3</v>
+        <v>3.3333333333333335</v>
       </c>
       <c r="D43" s="1">
-        <v>562.00000000000011</v>
+        <v>529.33333333333337</v>
       </c>
       <c r="E43" s="2">
-        <v>0.85910828025477926</v>
+        <v>0.8558340070061996</v>
       </c>
       <c r="F43" t="s">
         <v>5</v>
@@ -2079,19 +2079,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="B44">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C44" s="1">
-        <v>3</v>
+        <v>3.1666666666666665</v>
       </c>
       <c r="D44" s="1">
-        <v>565.00000000000011</v>
+        <v>532.5</v>
       </c>
       <c r="E44" s="2">
-        <v>0.86369426751592571</v>
+        <v>0.86095392077607291</v>
       </c>
       <c r="F44" t="s">
         <v>5</v>
@@ -2099,7 +2099,7 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="B45">
         <v>18</v>
@@ -2108,10 +2108,10 @@
         <v>3</v>
       </c>
       <c r="D45" s="1">
-        <v>568.00000000000011</v>
+        <v>535.5</v>
       </c>
       <c r="E45" s="2">
-        <v>0.86828025477707227</v>
+        <v>0.86580436540016348</v>
       </c>
       <c r="F45" t="s">
         <v>5</v>
@@ -2119,19 +2119,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>111</v>
+        <v>45</v>
       </c>
       <c r="B46">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C46" s="1">
-        <v>2.8333333333333335</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="D46" s="1">
-        <v>570.83333333333348</v>
+        <v>538.16666666666663</v>
       </c>
       <c r="E46" s="2">
-        <v>0.87261146496815511</v>
+        <v>0.87011587173268834</v>
       </c>
       <c r="F46" t="s">
         <v>5</v>
@@ -2139,19 +2139,19 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="B47">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C47" s="1">
-        <v>2.8333333333333335</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="D47" s="1">
-        <v>573.66666666666686</v>
+        <v>540.83333333333326</v>
       </c>
       <c r="E47" s="2">
-        <v>0.87694267515923796</v>
+        <v>0.8744273780652132</v>
       </c>
       <c r="F47" t="s">
         <v>5</v>
@@ -2159,19 +2159,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="B48">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C48" s="1">
-        <v>2.1666666666666665</v>
+        <v>2.5</v>
       </c>
       <c r="D48" s="1">
-        <v>575.83333333333348</v>
+        <v>543.33333333333326</v>
       </c>
       <c r="E48" s="2">
-        <v>0.88025477707006594</v>
+        <v>0.87846941525195532</v>
       </c>
       <c r="F48" t="s">
         <v>5</v>
@@ -2179,19 +2179,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>113</v>
+        <v>41</v>
       </c>
       <c r="B49">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C49" s="1">
-        <v>2</v>
+        <v>2.3333333333333335</v>
       </c>
       <c r="D49" s="1">
-        <v>577.83333333333348</v>
+        <v>545.66666666666663</v>
       </c>
       <c r="E49" s="2">
-        <v>0.88331210191083032</v>
+        <v>0.8822419832929147</v>
       </c>
       <c r="F49" t="s">
         <v>5</v>
@@ -2199,19 +2199,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="B50">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C50" s="1">
-        <v>2</v>
+        <v>2.1666666666666665</v>
       </c>
       <c r="D50" s="1">
-        <v>579.83333333333348</v>
+        <v>547.83333333333326</v>
       </c>
       <c r="E50" s="2">
-        <v>0.88636942675159469</v>
+        <v>0.88574508218809112</v>
       </c>
       <c r="F50" t="s">
         <v>5</v>
@@ -2219,19 +2219,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="B51">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C51" s="1">
-        <v>1.8333333333333333</v>
+        <v>2.1666666666666665</v>
       </c>
       <c r="D51" s="1">
-        <v>581.66666666666686</v>
+        <v>549.99999999999989</v>
       </c>
       <c r="E51" s="2">
-        <v>0.88917197452229535</v>
+        <v>0.88924818108326753</v>
       </c>
       <c r="F51" t="s">
         <v>5</v>
@@ -2239,19 +2239,19 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>116</v>
+        <v>40</v>
       </c>
       <c r="B52">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C52" s="1">
-        <v>1.8333333333333333</v>
+        <v>2</v>
       </c>
       <c r="D52" s="1">
-        <v>583.50000000000023</v>
+        <v>551.99999999999989</v>
       </c>
       <c r="E52" s="2">
-        <v>0.89197452229299601</v>
+        <v>0.89248181083266132</v>
       </c>
       <c r="F52" t="s">
         <v>5</v>
@@ -2259,19 +2259,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>117</v>
+        <v>19</v>
       </c>
       <c r="B53">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C53" s="1">
-        <v>1.8333333333333333</v>
+        <v>2</v>
       </c>
       <c r="D53" s="1">
-        <v>585.3333333333336</v>
+        <v>553.99999999999989</v>
       </c>
       <c r="E53" s="2">
-        <v>0.89477707006369678</v>
+        <v>0.89571544058205499</v>
       </c>
       <c r="F53" t="s">
         <v>5</v>
@@ -2279,7 +2279,7 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="B54">
         <v>11</v>
@@ -2288,10 +2288,10 @@
         <v>1.8333333333333333</v>
       </c>
       <c r="D54" s="1">
-        <v>587.16666666666697</v>
+        <v>555.83333333333326</v>
       </c>
       <c r="E54" s="2">
-        <v>0.89757961783439744</v>
+        <v>0.89867960118566592</v>
       </c>
       <c r="F54" t="s">
         <v>5</v>
@@ -2299,7 +2299,7 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>119</v>
+        <v>46</v>
       </c>
       <c r="B55">
         <v>11</v>
@@ -2308,10 +2308,10 @@
         <v>1.8333333333333333</v>
       </c>
       <c r="D55" s="1">
-        <v>589.00000000000034</v>
+        <v>557.66666666666663</v>
       </c>
       <c r="E55" s="2">
-        <v>0.90038216560509809</v>
+        <v>0.90164376178927685</v>
       </c>
       <c r="F55" t="s">
         <v>35</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="B56">
         <v>11</v>
@@ -2328,10 +2328,10 @@
         <v>1.8333333333333333</v>
       </c>
       <c r="D56" s="1">
-        <v>590.83333333333371</v>
+        <v>559.5</v>
       </c>
       <c r="E56" s="2">
-        <v>0.90318471337579886</v>
+        <v>0.9046079223928879</v>
       </c>
       <c r="F56" t="s">
         <v>35</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="B57">
         <v>10</v>
@@ -2348,10 +2348,10 @@
         <v>1.6666666666666667</v>
       </c>
       <c r="D57" s="1">
-        <v>592.50000000000034</v>
+        <v>561.16666666666663</v>
       </c>
       <c r="E57" s="2">
-        <v>0.9057324840764357</v>
+        <v>0.90730261385071587</v>
       </c>
       <c r="F57" t="s">
         <v>35</v>
@@ -2359,7 +2359,7 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>46</v>
+        <v>127</v>
       </c>
       <c r="B58">
         <v>10</v>
@@ -2368,10 +2368,10 @@
         <v>1.6666666666666667</v>
       </c>
       <c r="D58" s="1">
-        <v>594.16666666666697</v>
+        <v>562.83333333333326</v>
       </c>
       <c r="E58" s="2">
-        <v>0.90828025477707264</v>
+        <v>0.90999730530854384</v>
       </c>
       <c r="F58" t="s">
         <v>35</v>
@@ -2379,7 +2379,7 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>32</v>
+        <v>122</v>
       </c>
       <c r="B59">
         <v>10</v>
@@ -2388,10 +2388,10 @@
         <v>1.6666666666666667</v>
       </c>
       <c r="D59" s="1">
-        <v>595.8333333333336</v>
+        <v>564.49999999999989</v>
       </c>
       <c r="E59" s="2">
-        <v>0.91082802547770947</v>
+        <v>0.91269199676637192</v>
       </c>
       <c r="F59" t="s">
         <v>35</v>
@@ -2399,7 +2399,7 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>40</v>
+        <v>126</v>
       </c>
       <c r="B60">
         <v>10</v>
@@ -2408,10 +2408,10 @@
         <v>1.6666666666666667</v>
       </c>
       <c r="D60" s="1">
-        <v>597.50000000000023</v>
+        <v>566.16666666666652</v>
       </c>
       <c r="E60" s="2">
-        <v>0.91337579617834641</v>
+        <v>0.91538668822419988</v>
       </c>
       <c r="F60" t="s">
         <v>35</v>
@@ -2419,7 +2419,7 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="B61">
         <v>9</v>
@@ -2428,10 +2428,10 @@
         <v>1.5</v>
       </c>
       <c r="D61" s="1">
-        <v>599.00000000000023</v>
+        <v>567.66666666666652</v>
       </c>
       <c r="E61" s="2">
-        <v>0.91566878980891964</v>
+        <v>0.91781191053624522</v>
       </c>
       <c r="F61" t="s">
         <v>35</v>
@@ -2439,7 +2439,7 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="B62">
         <v>9</v>
@@ -2448,10 +2448,10 @@
         <v>1.5</v>
       </c>
       <c r="D62" s="1">
-        <v>600.50000000000023</v>
+        <v>569.16666666666652</v>
       </c>
       <c r="E62" s="2">
-        <v>0.91796178343949297</v>
+        <v>0.92023713284829045</v>
       </c>
       <c r="F62" t="s">
         <v>35</v>
@@ -2459,19 +2459,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="B63">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C63" s="1">
-        <v>1.3333333333333333</v>
+        <v>1.5</v>
       </c>
       <c r="D63" s="1">
-        <v>601.8333333333336</v>
+        <v>570.66666666666652</v>
       </c>
       <c r="E63" s="2">
-        <v>0.92000000000000248</v>
+        <v>0.92266235516033579</v>
       </c>
       <c r="F63" t="s">
         <v>35</v>
@@ -2479,7 +2479,7 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>121</v>
+        <v>52</v>
       </c>
       <c r="B64">
         <v>8</v>
@@ -2488,10 +2488,10 @@
         <v>1.3333333333333333</v>
       </c>
       <c r="D64" s="1">
-        <v>603.16666666666697</v>
+        <v>571.99999999999989</v>
       </c>
       <c r="E64" s="2">
-        <v>0.9220382165605121</v>
+        <v>0.92481810832659828</v>
       </c>
       <c r="F64" t="s">
         <v>35</v>
@@ -2499,7 +2499,7 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>122</v>
+        <v>162</v>
       </c>
       <c r="B65">
         <v>8</v>
@@ -2508,10 +2508,10 @@
         <v>1.3333333333333333</v>
       </c>
       <c r="D65" s="1">
-        <v>604.50000000000034</v>
+        <v>573.33333333333326</v>
       </c>
       <c r="E65" s="2">
-        <v>0.92407643312102172</v>
+        <v>0.92697386149286087</v>
       </c>
       <c r="F65" t="s">
         <v>35</v>
@@ -2519,19 +2519,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="B66">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C66" s="1">
-        <v>1.1666666666666667</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="D66" s="1">
-        <v>605.66666666666697</v>
+        <v>574.66666666666663</v>
       </c>
       <c r="E66" s="2">
-        <v>0.92585987261146763</v>
+        <v>0.92912961465912336</v>
       </c>
       <c r="F66" t="s">
         <v>35</v>
@@ -2539,7 +2539,7 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="B67">
         <v>7</v>
@@ -2548,10 +2548,10 @@
         <v>1.1666666666666667</v>
       </c>
       <c r="D67" s="1">
-        <v>606.8333333333336</v>
+        <v>575.83333333333326</v>
       </c>
       <c r="E67" s="2">
-        <v>0.92764331210191342</v>
+        <v>0.93101589867960299</v>
       </c>
       <c r="F67" t="s">
         <v>35</v>
@@ -2559,7 +2559,7 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B68">
         <v>7</v>
@@ -2568,10 +2568,10 @@
         <v>1.1666666666666667</v>
       </c>
       <c r="D68" s="1">
-        <v>608.00000000000023</v>
+        <v>576.99999999999989</v>
       </c>
       <c r="E68" s="2">
-        <v>0.92942675159235921</v>
+        <v>0.93290218270008252</v>
       </c>
       <c r="F68" t="s">
         <v>35</v>
@@ -2579,19 +2579,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>125</v>
+        <v>22</v>
       </c>
       <c r="B69">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C69" s="1">
-        <v>1.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="D69" s="1">
-        <v>609.16666666666686</v>
+        <v>577.99999999999989</v>
       </c>
       <c r="E69" s="2">
-        <v>0.93121019108280501</v>
+        <v>0.93451899757477941</v>
       </c>
       <c r="F69" t="s">
         <v>35</v>
@@ -2602,16 +2602,16 @@
         <v>30</v>
       </c>
       <c r="B70">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C70" s="1">
-        <v>1.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="D70" s="1">
-        <v>610.33333333333348</v>
+        <v>578.99999999999989</v>
       </c>
       <c r="E70" s="2">
-        <v>0.9329936305732508</v>
+        <v>0.93613581244947619</v>
       </c>
       <c r="F70" t="s">
         <v>35</v>
@@ -2619,7 +2619,7 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>31</v>
+        <v>119</v>
       </c>
       <c r="B71">
         <v>6</v>
@@ -2628,10 +2628,10 @@
         <v>1</v>
       </c>
       <c r="D71" s="1">
-        <v>611.33333333333348</v>
+        <v>579.99999999999989</v>
       </c>
       <c r="E71" s="2">
-        <v>0.93452229299363299</v>
+        <v>0.93775262732417308</v>
       </c>
       <c r="F71" t="s">
         <v>35</v>
@@ -2639,7 +2639,7 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>126</v>
+        <v>113</v>
       </c>
       <c r="B72">
         <v>6</v>
@@ -2648,10 +2648,10 @@
         <v>1</v>
       </c>
       <c r="D72" s="1">
-        <v>612.33333333333348</v>
+        <v>580.99999999999989</v>
       </c>
       <c r="E72" s="2">
-        <v>0.93605095541401517</v>
+        <v>0.93936944219886997</v>
       </c>
       <c r="F72" t="s">
         <v>35</v>
@@ -2659,7 +2659,7 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>127</v>
+        <v>76</v>
       </c>
       <c r="B73">
         <v>6</v>
@@ -2668,10 +2668,10 @@
         <v>1</v>
       </c>
       <c r="D73" s="1">
-        <v>613.33333333333348</v>
+        <v>581.99999999999989</v>
       </c>
       <c r="E73" s="2">
-        <v>0.93757961783439736</v>
+        <v>0.94098625707356676</v>
       </c>
       <c r="F73" t="s">
         <v>35</v>
@@ -2679,7 +2679,7 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="B74">
         <v>6</v>
@@ -2688,10 +2688,10 @@
         <v>1</v>
       </c>
       <c r="D74" s="1">
-        <v>614.33333333333348</v>
+        <v>582.99999999999989</v>
       </c>
       <c r="E74" s="2">
-        <v>0.93910828025477944</v>
+        <v>0.94260307194826365</v>
       </c>
       <c r="F74" t="s">
         <v>35</v>
@@ -2699,7 +2699,7 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B75">
         <v>6</v>
@@ -2708,10 +2708,10 @@
         <v>1</v>
       </c>
       <c r="D75" s="1">
-        <v>615.33333333333348</v>
+        <v>583.99999999999989</v>
       </c>
       <c r="E75" s="2">
-        <v>0.94063694267516162</v>
+        <v>0.94421988682296054</v>
       </c>
       <c r="F75" t="s">
         <v>35</v>
@@ -2719,19 +2719,19 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="B76">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C76" s="1">
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="D76" s="1">
-        <v>616.33333333333348</v>
+        <v>584.83333333333326</v>
       </c>
       <c r="E76" s="2">
-        <v>0.94216560509554381</v>
+        <v>0.94556723255187458</v>
       </c>
       <c r="F76" t="s">
         <v>35</v>
@@ -2739,7 +2739,7 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>60</v>
+        <v>115</v>
       </c>
       <c r="B77">
         <v>5</v>
@@ -2748,10 +2748,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D77" s="1">
-        <v>617.16666666666686</v>
+        <v>585.66666666666663</v>
       </c>
       <c r="E77" s="2">
-        <v>0.94343949044586239</v>
+        <v>0.94691457828078873</v>
       </c>
       <c r="F77" t="s">
         <v>35</v>
@@ -2759,7 +2759,7 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>130</v>
+        <v>55</v>
       </c>
       <c r="B78">
         <v>5</v>
@@ -2768,10 +2768,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D78" s="1">
-        <v>618.00000000000023</v>
+        <v>586.5</v>
       </c>
       <c r="E78" s="2">
-        <v>0.94471337579618087</v>
+        <v>0.94826192400970277</v>
       </c>
       <c r="F78" t="s">
         <v>35</v>
@@ -2779,7 +2779,7 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>55</v>
+        <v>134</v>
       </c>
       <c r="B79">
         <v>5</v>
@@ -2788,10 +2788,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D79" s="1">
-        <v>618.8333333333336</v>
+        <v>587.33333333333337</v>
       </c>
       <c r="E79" s="2">
-        <v>0.94598726114649945</v>
+        <v>0.94960926973861692</v>
       </c>
       <c r="F79" t="s">
         <v>35</v>
@@ -2799,7 +2799,7 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="B80">
         <v>5</v>
@@ -2808,70 +2808,70 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="D80" s="1">
-        <v>619.66666666666697</v>
+        <v>588.16666666666674</v>
       </c>
       <c r="E80" s="2">
-        <v>0.94726114649681792</v>
+        <v>0.95095661546753096</v>
       </c>
       <c r="F80" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>50</v>
+        <v>121</v>
       </c>
       <c r="B81">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C81" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D81" s="1">
-        <v>620.50000000000034</v>
+        <v>588.83333333333337</v>
       </c>
       <c r="E81" s="2">
-        <v>0.9485350318471365</v>
+        <v>0.95203449205066215</v>
       </c>
       <c r="F81" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>72</v>
+        <v>42</v>
       </c>
       <c r="B82">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C82" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="D82" s="1">
-        <v>621.33333333333371</v>
+        <v>589.5</v>
       </c>
       <c r="E82" s="2">
-        <v>0.94980891719745497</v>
+        <v>0.95311236863379334</v>
       </c>
       <c r="F82" t="s">
-        <v>35</v>
+        <v>51</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>42</v>
+        <v>139</v>
       </c>
       <c r="B83">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C83" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="D83" s="1">
-        <v>622.16666666666708</v>
+        <v>590</v>
       </c>
       <c r="E83" s="2">
-        <v>0.95108280254777355</v>
+        <v>0.95392077607114178</v>
       </c>
       <c r="F83" t="s">
         <v>51</v>
@@ -2879,19 +2879,19 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="B84">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C84" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="D84" s="1">
-        <v>623.00000000000045</v>
+        <v>590.5</v>
       </c>
       <c r="E84" s="2">
-        <v>0.95235668789809202</v>
+        <v>0.95472918350849023</v>
       </c>
       <c r="F84" t="s">
         <v>51</v>
@@ -2899,19 +2899,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="B85">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C85" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="D85" s="1">
-        <v>623.83333333333383</v>
+        <v>591</v>
       </c>
       <c r="E85" s="2">
-        <v>0.95363057324841061</v>
+        <v>0.95553759094583868</v>
       </c>
       <c r="F85" t="s">
         <v>51</v>
@@ -2919,19 +2919,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>134</v>
+        <v>50</v>
       </c>
       <c r="B86">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C86" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="D86" s="1">
-        <v>624.6666666666672</v>
+        <v>591.5</v>
       </c>
       <c r="E86" s="2">
-        <v>0.95490445859872919</v>
+        <v>0.95634599838318701</v>
       </c>
       <c r="F86" t="s">
         <v>51</v>
@@ -2939,19 +2939,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>97</v>
+        <v>140</v>
       </c>
       <c r="B87">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C87" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="D87" s="1">
-        <v>625.50000000000057</v>
+        <v>592</v>
       </c>
       <c r="E87" s="2">
-        <v>0.95617834394904766</v>
+        <v>0.95715440582053546</v>
       </c>
       <c r="F87" t="s">
         <v>51</v>
@@ -2959,19 +2959,19 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B88">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C88" s="1">
-        <v>0.83333333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="D88" s="1">
-        <v>626.33333333333394</v>
+        <v>592.5</v>
       </c>
       <c r="E88" s="2">
-        <v>0.95745222929936624</v>
+        <v>0.95796281325788391</v>
       </c>
       <c r="F88" t="s">
         <v>51</v>
@@ -2979,19 +2979,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="B89">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C89" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="D89" s="1">
-        <v>627.00000000000057</v>
+        <v>593</v>
       </c>
       <c r="E89" s="2">
-        <v>0.95847133757962089</v>
+        <v>0.95877122069523235</v>
       </c>
       <c r="F89" t="s">
         <v>51</v>
@@ -2999,19 +2999,19 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="B90">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C90" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="D90" s="1">
-        <v>627.6666666666672</v>
+        <v>593.5</v>
       </c>
       <c r="E90" s="2">
-        <v>0.95949044585987564</v>
+        <v>0.9595796281325808</v>
       </c>
       <c r="F90" t="s">
         <v>51</v>
@@ -3019,19 +3019,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B91">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C91" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="D91" s="1">
-        <v>628.33333333333383</v>
+        <v>594</v>
       </c>
       <c r="E91" s="2">
-        <v>0.96050955414013039</v>
+        <v>0.96038803556992913</v>
       </c>
       <c r="F91" t="s">
         <v>51</v>
@@ -3039,19 +3039,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>139</v>
+        <v>58</v>
       </c>
       <c r="B92">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C92" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="D92" s="1">
-        <v>629.00000000000045</v>
+        <v>594.5</v>
       </c>
       <c r="E92" s="2">
-        <v>0.96152866242038504</v>
+        <v>0.96119644300727758</v>
       </c>
       <c r="F92" t="s">
         <v>51</v>
@@ -3059,19 +3059,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>34</v>
+        <v>136</v>
       </c>
       <c r="B93">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C93" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="D93" s="1">
-        <v>629.66666666666708</v>
+        <v>595</v>
       </c>
       <c r="E93" s="2">
-        <v>0.96254777070063979</v>
+        <v>0.96200485044462603</v>
       </c>
       <c r="F93" t="s">
         <v>51</v>
@@ -3079,19 +3079,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>140</v>
+        <v>39</v>
       </c>
       <c r="B94">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C94" s="1">
-        <v>0.66666666666666663</v>
+        <v>0.5</v>
       </c>
       <c r="D94" s="1">
-        <v>630.33333333333371</v>
+        <v>595.5</v>
       </c>
       <c r="E94" s="2">
-        <v>0.96356687898089455</v>
+        <v>0.96281325788197447</v>
       </c>
       <c r="F94" t="s">
         <v>51</v>
@@ -3099,19 +3099,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>141</v>
+        <v>208</v>
       </c>
       <c r="B95">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C95" s="1">
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D95" s="1">
-        <v>630.83333333333371</v>
+        <v>595.83333333333337</v>
       </c>
       <c r="E95" s="2">
-        <v>0.96433121019108559</v>
+        <v>0.96335219617354018</v>
       </c>
       <c r="F95" t="s">
         <v>51</v>
@@ -3119,39 +3119,39 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>39</v>
+        <v>187</v>
       </c>
       <c r="B96">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C96" s="1">
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D96" s="1">
-        <v>631.33333333333371</v>
+        <v>596.16666666666674</v>
       </c>
       <c r="E96" s="2">
-        <v>0.96509554140127674</v>
+        <v>0.96389113446510577</v>
       </c>
       <c r="F96" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A97" s="3">
-        <v>91351642000</v>
+      <c r="A97" s="3" t="s">
+        <v>209</v>
       </c>
       <c r="B97">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C97" s="1">
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D97" s="1">
-        <v>631.83333333333371</v>
+        <v>596.50000000000011</v>
       </c>
       <c r="E97" s="2">
-        <v>0.96585987261146777</v>
+        <v>0.96443007275667147</v>
       </c>
       <c r="F97" t="s">
         <v>51</v>
@@ -3159,19 +3159,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>142</v>
+        <v>34</v>
       </c>
       <c r="B98">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C98" s="1">
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D98" s="1">
-        <v>632.33333333333371</v>
+        <v>596.83333333333348</v>
       </c>
       <c r="E98" s="2">
-        <v>0.96662420382165892</v>
+        <v>0.96496901104823718</v>
       </c>
       <c r="F98" t="s">
         <v>51</v>
@@ -3179,19 +3179,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>69</v>
+        <v>170</v>
       </c>
       <c r="B99">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C99" s="1">
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D99" s="1">
-        <v>632.83333333333371</v>
+        <v>597.16666666666686</v>
       </c>
       <c r="E99" s="2">
-        <v>0.96738853503184996</v>
+        <v>0.96550794933980288</v>
       </c>
       <c r="F99" t="s">
         <v>51</v>
@@ -3199,19 +3199,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>143</v>
+        <v>210</v>
       </c>
       <c r="B100">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C100" s="1">
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D100" s="1">
-        <v>633.33333333333371</v>
+        <v>597.50000000000023</v>
       </c>
       <c r="E100" s="2">
-        <v>0.968152866242041</v>
+        <v>0.96604688763136848</v>
       </c>
       <c r="F100" t="s">
         <v>51</v>
@@ -3219,19 +3219,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B101">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C101" s="1">
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D101" s="1">
-        <v>633.83333333333371</v>
+        <v>597.8333333333336</v>
       </c>
       <c r="E101" s="2">
-        <v>0.96891719745223215</v>
+        <v>0.96658582592293418</v>
       </c>
       <c r="F101" t="s">
         <v>51</v>
@@ -3239,19 +3239,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>67</v>
+        <v>137</v>
       </c>
       <c r="B102">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C102" s="1">
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D102" s="1">
-        <v>634.33333333333371</v>
+        <v>598.16666666666697</v>
       </c>
       <c r="E102" s="2">
-        <v>0.96968152866242319</v>
+        <v>0.96712476421449989</v>
       </c>
       <c r="F102" t="s">
         <v>51</v>
@@ -3259,19 +3259,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>145</v>
+        <v>164</v>
       </c>
       <c r="B103">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C103" s="1">
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D103" s="1">
-        <v>634.83333333333371</v>
+        <v>598.50000000000034</v>
       </c>
       <c r="E103" s="2">
-        <v>0.97044585987261434</v>
+        <v>0.96766370250606559</v>
       </c>
       <c r="F103" t="s">
         <v>51</v>
@@ -3279,19 +3279,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B104">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C104" s="1">
-        <v>0.5</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D104" s="1">
-        <v>635.33333333333371</v>
+        <v>598.83333333333371</v>
       </c>
       <c r="E104" s="2">
-        <v>0.97121019108280537</v>
+        <v>0.96820264079763119</v>
       </c>
       <c r="F104" t="s">
         <v>51</v>
@@ -3299,7 +3299,7 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="B105">
         <v>2</v>
@@ -3308,10 +3308,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D105" s="1">
-        <v>635.66666666666708</v>
+        <v>599.16666666666708</v>
       </c>
       <c r="E105" s="2">
-        <v>0.97171974522293281</v>
+        <v>0.96874157908919689</v>
       </c>
       <c r="F105" t="s">
         <v>51</v>
@@ -3319,7 +3319,7 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>37</v>
+        <v>176</v>
       </c>
       <c r="B106">
         <v>2</v>
@@ -3328,10 +3328,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D106" s="1">
-        <v>636.00000000000045</v>
+        <v>599.50000000000045</v>
       </c>
       <c r="E106" s="2">
-        <v>0.97222929936306024</v>
+        <v>0.9692805173807626</v>
       </c>
       <c r="F106" t="s">
         <v>51</v>
@@ -3339,7 +3339,7 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="B107">
         <v>2</v>
@@ -3348,10 +3348,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D107" s="1">
-        <v>636.33333333333383</v>
+        <v>599.83333333333383</v>
       </c>
       <c r="E107" s="2">
-        <v>0.97273885350318767</v>
+        <v>0.9698194556723283</v>
       </c>
       <c r="F107" t="s">
         <v>51</v>
@@ -3359,7 +3359,7 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>74</v>
+        <v>169</v>
       </c>
       <c r="B108">
         <v>2</v>
@@ -3368,10 +3368,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D108" s="1">
-        <v>636.6666666666672</v>
+        <v>600.1666666666672</v>
       </c>
       <c r="E108" s="2">
-        <v>0.97324840764331522</v>
+        <v>0.97035839396389401</v>
       </c>
       <c r="F108" t="s">
         <v>51</v>
@@ -3379,7 +3379,7 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>149</v>
+        <v>195</v>
       </c>
       <c r="B109">
         <v>2</v>
@@ -3388,10 +3388,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D109" s="1">
-        <v>637.00000000000057</v>
+        <v>600.50000000000057</v>
       </c>
       <c r="E109" s="2">
-        <v>0.97375796178344265</v>
+        <v>0.9708973322554596</v>
       </c>
       <c r="F109" t="s">
         <v>51</v>
@@ -3399,7 +3399,7 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="B110">
         <v>2</v>
@@ -3408,10 +3408,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D110" s="1">
-        <v>637.33333333333394</v>
+        <v>600.83333333333394</v>
       </c>
       <c r="E110" s="2">
-        <v>0.97426751592357008</v>
+        <v>0.9714362705470253</v>
       </c>
       <c r="F110" t="s">
         <v>51</v>
@@ -3419,7 +3419,7 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="3" t="s">
-        <v>48</v>
+        <v>142</v>
       </c>
       <c r="B111">
         <v>2</v>
@@ -3428,10 +3428,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D111" s="1">
-        <v>637.66666666666731</v>
+        <v>601.16666666666731</v>
       </c>
       <c r="E111" s="2">
-        <v>0.97477707006369751</v>
+        <v>0.97197520883859101</v>
       </c>
       <c r="F111" t="s">
         <v>51</v>
@@ -3439,7 +3439,7 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="B112">
         <v>2</v>
@@ -3448,18 +3448,18 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D112" s="1">
-        <v>638.00000000000068</v>
+        <v>601.50000000000068</v>
       </c>
       <c r="E112" s="2">
-        <v>0.97528662420382495</v>
+        <v>0.97251414713015671</v>
       </c>
       <c r="F112" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A113" s="3">
-        <v>9805657723</v>
+      <c r="A113" s="3" t="s">
+        <v>152</v>
       </c>
       <c r="B113">
         <v>2</v>
@@ -3468,10 +3468,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D113" s="1">
-        <v>638.33333333333405</v>
+        <v>601.83333333333405</v>
       </c>
       <c r="E113" s="2">
-        <v>0.97579617834395238</v>
+        <v>0.97305308542172231</v>
       </c>
       <c r="F113" t="s">
         <v>51</v>
@@ -3479,7 +3479,7 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="B114">
         <v>2</v>
@@ -3488,10 +3488,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D114" s="1">
-        <v>638.66666666666742</v>
+        <v>602.16666666666742</v>
       </c>
       <c r="E114" s="2">
-        <v>0.97630573248407981</v>
+        <v>0.97359202371328801</v>
       </c>
       <c r="F114" t="s">
         <v>51</v>
@@ -3499,7 +3499,7 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>151</v>
+        <v>172</v>
       </c>
       <c r="B115">
         <v>2</v>
@@ -3508,10 +3508,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D115" s="1">
-        <v>639.0000000000008</v>
+        <v>602.5000000000008</v>
       </c>
       <c r="E115" s="2">
-        <v>0.97681528662420725</v>
+        <v>0.97413096200485372</v>
       </c>
       <c r="F115" t="s">
         <v>51</v>
@@ -3519,7 +3519,7 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>152</v>
+        <v>31</v>
       </c>
       <c r="B116">
         <v>2</v>
@@ -3528,10 +3528,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D116" s="1">
-        <v>639.33333333333417</v>
+        <v>602.83333333333417</v>
       </c>
       <c r="E116" s="2">
-        <v>0.97732484076433479</v>
+        <v>0.97466990029641942</v>
       </c>
       <c r="F116" t="s">
         <v>51</v>
@@ -3539,7 +3539,7 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B117">
         <v>2</v>
@@ -3548,10 +3548,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D117" s="1">
-        <v>639.66666666666754</v>
+        <v>603.16666666666754</v>
       </c>
       <c r="E117" s="2">
-        <v>0.97783439490446222</v>
+        <v>0.97520883858798502</v>
       </c>
       <c r="F117" t="s">
         <v>51</v>
@@ -3559,7 +3559,7 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>154</v>
+        <v>62</v>
       </c>
       <c r="B118">
         <v>2</v>
@@ -3568,10 +3568,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D118" s="1">
-        <v>640.00000000000091</v>
+        <v>603.50000000000091</v>
       </c>
       <c r="E118" s="2">
-        <v>0.97834394904458966</v>
+        <v>0.97574777687955072</v>
       </c>
       <c r="F118" t="s">
         <v>51</v>
@@ -3579,7 +3579,7 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="B119">
         <v>2</v>
@@ -3588,10 +3588,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D119" s="1">
-        <v>640.33333333333428</v>
+        <v>603.83333333333428</v>
       </c>
       <c r="E119" s="2">
-        <v>0.97885350318471709</v>
+        <v>0.97628671517111643</v>
       </c>
       <c r="F119" t="s">
         <v>51</v>
@@ -3599,7 +3599,7 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>59</v>
+        <v>185</v>
       </c>
       <c r="B120">
         <v>2</v>
@@ -3608,10 +3608,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D120" s="1">
-        <v>640.66666666666765</v>
+        <v>604.16666666666765</v>
       </c>
       <c r="E120" s="2">
-        <v>0.97936305732484452</v>
+        <v>0.97682565346268213</v>
       </c>
       <c r="F120" t="s">
         <v>51</v>
@@ -3619,7 +3619,7 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="B121">
         <v>2</v>
@@ -3628,10 +3628,10 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D121" s="1">
-        <v>641.00000000000102</v>
+        <v>604.50000000000102</v>
       </c>
       <c r="E121" s="2">
-        <v>0.97987261146497195</v>
+        <v>0.97736459175424772</v>
       </c>
       <c r="F121" t="s">
         <v>51</v>
@@ -3639,7 +3639,7 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="B122">
         <v>2</v>
@@ -3648,18 +3648,18 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D122" s="1">
-        <v>641.33333333333439</v>
+        <v>604.83333333333439</v>
       </c>
       <c r="E122" s="2">
-        <v>0.98038216560509939</v>
+        <v>0.97790353004581343</v>
       </c>
       <c r="F122" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>158</v>
+        <v>70</v>
       </c>
       <c r="B123">
         <v>2</v>
@@ -3668,18 +3668,18 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D123" s="1">
-        <v>641.66666666666777</v>
+        <v>605.16666666666777</v>
       </c>
       <c r="E123" s="2">
-        <v>0.98089171974522693</v>
+        <v>0.97844246833737913</v>
       </c>
       <c r="F123" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="B124">
         <v>2</v>
@@ -3688,18 +3688,18 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D124" s="1">
-        <v>642.00000000000114</v>
+        <v>605.50000000000114</v>
       </c>
       <c r="E124" s="2">
-        <v>0.98140127388535436</v>
+        <v>0.97898140662894484</v>
       </c>
       <c r="F124" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>73</v>
+        <v>145</v>
       </c>
       <c r="B125">
         <v>2</v>
@@ -3708,98 +3708,98 @@
         <v>0.33333333333333331</v>
       </c>
       <c r="D125" s="1">
-        <v>642.33333333333451</v>
+        <v>605.83333333333451</v>
       </c>
       <c r="E125" s="2">
-        <v>0.9819108280254818</v>
+        <v>0.97952034492051043</v>
       </c>
       <c r="F125" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="B126">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C126" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D126" s="1">
-        <v>642.50000000000114</v>
+        <v>606.16666666666788</v>
       </c>
       <c r="E126" s="2">
-        <v>0.9821656050955454</v>
+        <v>0.98005928321207614</v>
       </c>
       <c r="F126" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>161</v>
+        <v>129</v>
       </c>
       <c r="B127">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C127" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D127" s="1">
-        <v>642.66666666666777</v>
+        <v>606.50000000000125</v>
       </c>
       <c r="E127" s="2">
-        <v>0.98242038216560901</v>
+        <v>0.98059822150364184</v>
       </c>
       <c r="F127" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>162</v>
+        <v>66</v>
       </c>
       <c r="B128">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C128" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D128" s="1">
-        <v>642.83333333333439</v>
+        <v>606.83333333333462</v>
       </c>
       <c r="E128" s="2">
-        <v>0.98267515923567272</v>
+        <v>0.98113715979520755</v>
       </c>
       <c r="F128" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="B129">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C129" s="1">
-        <v>0.16666666666666666</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="D129" s="1">
-        <v>643.00000000000102</v>
+        <v>607.16666666666799</v>
       </c>
       <c r="E129" s="2">
-        <v>0.98292993630573633</v>
+        <v>0.98167609808677314</v>
       </c>
       <c r="F129" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>164</v>
+        <v>211</v>
       </c>
       <c r="B130">
         <v>1</v>
@@ -3808,18 +3808,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D130" s="1">
-        <v>643.16666666666765</v>
+        <v>607.33333333333462</v>
       </c>
       <c r="E130" s="2">
-        <v>0.98318471337579993</v>
+        <v>0.98194556723255599</v>
       </c>
       <c r="F130" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="3" t="s">
-        <v>165</v>
+        <v>188</v>
       </c>
       <c r="B131">
         <v>1</v>
@@ -3828,18 +3828,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D131" s="1">
-        <v>643.33333333333428</v>
+        <v>607.50000000000125</v>
       </c>
       <c r="E131" s="2">
-        <v>0.98343949044586365</v>
+        <v>0.98221503637833874</v>
       </c>
       <c r="F131" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="B132">
         <v>1</v>
@@ -3848,18 +3848,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D132" s="1">
-        <v>643.50000000000091</v>
+        <v>607.66666666666788</v>
       </c>
       <c r="E132" s="2">
-        <v>0.98369426751592726</v>
+        <v>0.98248450552412148</v>
       </c>
       <c r="F132" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>167</v>
+        <v>49</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -3868,18 +3868,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D133" s="1">
-        <v>643.66666666666754</v>
+        <v>607.83333333333451</v>
       </c>
       <c r="E133" s="2">
-        <v>0.98394904458599086</v>
+        <v>0.98275397466990422</v>
       </c>
       <c r="F133" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>65</v>
+        <v>155</v>
       </c>
       <c r="B134">
         <v>1</v>
@@ -3888,18 +3888,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D134" s="1">
-        <v>643.83333333333417</v>
+        <v>608.00000000000114</v>
       </c>
       <c r="E134" s="2">
-        <v>0.98420382165605447</v>
+        <v>0.98302344381568696</v>
       </c>
       <c r="F134" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>168</v>
+        <v>60</v>
       </c>
       <c r="B135">
         <v>1</v>
@@ -3908,18 +3908,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D135" s="1">
-        <v>644.0000000000008</v>
+        <v>608.16666666666777</v>
       </c>
       <c r="E135" s="2">
-        <v>0.98445859872611818</v>
+        <v>0.9832929129614697</v>
       </c>
       <c r="F135" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>169</v>
+        <v>212</v>
       </c>
       <c r="B136">
         <v>1</v>
@@ -3928,18 +3928,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D136" s="1">
-        <v>644.16666666666742</v>
+        <v>608.33333333333439</v>
       </c>
       <c r="E136" s="2">
-        <v>0.98471337579618179</v>
+        <v>0.98356238210725244</v>
       </c>
       <c r="F136" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>170</v>
+        <v>56</v>
       </c>
       <c r="B137">
         <v>1</v>
@@ -3948,18 +3948,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D137" s="1">
-        <v>644.33333333333405</v>
+        <v>608.50000000000102</v>
       </c>
       <c r="E137" s="2">
-        <v>0.98496815286624539</v>
+        <v>0.98383185125303518</v>
       </c>
       <c r="F137" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>171</v>
+        <v>213</v>
       </c>
       <c r="B138">
         <v>1</v>
@@ -3968,18 +3968,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D138" s="1">
-        <v>644.50000000000068</v>
+        <v>608.66666666666765</v>
       </c>
       <c r="E138" s="2">
-        <v>0.98522292993630911</v>
+        <v>0.98410132039881792</v>
       </c>
       <c r="F138" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B139">
         <v>1</v>
@@ -3988,18 +3988,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D139" s="1">
-        <v>644.66666666666731</v>
+        <v>608.83333333333428</v>
       </c>
       <c r="E139" s="2">
-        <v>0.98547770700637272</v>
+        <v>0.98437078954460067</v>
       </c>
       <c r="F139" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="B140">
         <v>1</v>
@@ -4008,18 +4008,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D140" s="1">
-        <v>644.83333333333394</v>
+        <v>609.00000000000091</v>
       </c>
       <c r="E140" s="2">
-        <v>0.98573248407643632</v>
+        <v>0.98464025869038341</v>
       </c>
       <c r="F140" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>174</v>
+        <v>214</v>
       </c>
       <c r="B141">
         <v>1</v>
@@ -4028,18 +4028,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D141" s="1">
-        <v>645.00000000000057</v>
+        <v>609.16666666666754</v>
       </c>
       <c r="E141" s="2">
-        <v>0.98598726114649993</v>
+        <v>0.98490972783616615</v>
       </c>
       <c r="F141" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>175</v>
+        <v>215</v>
       </c>
       <c r="B142">
         <v>1</v>
@@ -4048,18 +4048,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D142" s="1">
-        <v>645.1666666666672</v>
+        <v>609.33333333333417</v>
       </c>
       <c r="E142" s="2">
-        <v>0.98624203821656364</v>
+        <v>0.98517919698194889</v>
       </c>
       <c r="F142" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>176</v>
+        <v>216</v>
       </c>
       <c r="B143">
         <v>1</v>
@@ -4068,18 +4068,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D143" s="1">
-        <v>645.33333333333383</v>
+        <v>609.5000000000008</v>
       </c>
       <c r="E143" s="2">
-        <v>0.98649681528662725</v>
+        <v>0.98544866612773163</v>
       </c>
       <c r="F143" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>177</v>
+        <v>217</v>
       </c>
       <c r="B144">
         <v>1</v>
@@ -4088,18 +4088,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D144" s="1">
-        <v>645.50000000000045</v>
+        <v>609.66666666666742</v>
       </c>
       <c r="E144" s="2">
-        <v>0.98675159235669085</v>
+        <v>0.98571813527351437</v>
       </c>
       <c r="F144" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="B145">
         <v>1</v>
@@ -4108,18 +4108,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D145" s="1">
-        <v>645.66666666666708</v>
+        <v>609.83333333333405</v>
       </c>
       <c r="E145" s="2">
-        <v>0.98700636942675457</v>
+        <v>0.98598760441929711</v>
       </c>
       <c r="F145" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="B146">
         <v>1</v>
@@ -4128,18 +4128,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D146" s="1">
-        <v>645.83333333333371</v>
+        <v>610.00000000000068</v>
       </c>
       <c r="E146" s="2">
-        <v>0.98726114649681818</v>
+        <v>0.98625707356507986</v>
       </c>
       <c r="F146" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>180</v>
+        <v>57</v>
       </c>
       <c r="B147">
         <v>1</v>
@@ -4148,18 +4148,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D147" s="1">
-        <v>646.00000000000034</v>
+        <v>610.16666666666731</v>
       </c>
       <c r="E147" s="2">
-        <v>0.98751592356688178</v>
+        <v>0.9865265427108626</v>
       </c>
       <c r="F147" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="3" t="s">
-        <v>181</v>
+        <v>160</v>
       </c>
       <c r="B148">
         <v>1</v>
@@ -4168,18 +4168,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D148" s="1">
-        <v>646.16666666666697</v>
+        <v>610.33333333333394</v>
       </c>
       <c r="E148" s="2">
-        <v>0.98777070063694539</v>
+        <v>0.98679601185664534</v>
       </c>
       <c r="F148" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>49</v>
+        <v>154</v>
       </c>
       <c r="B149">
         <v>1</v>
@@ -4188,18 +4188,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D149" s="1">
-        <v>646.3333333333336</v>
+        <v>610.50000000000057</v>
       </c>
       <c r="E149" s="2">
-        <v>0.9880254777070091</v>
+        <v>0.98706548100242819</v>
       </c>
       <c r="F149" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B150">
         <v>1</v>
@@ -4208,18 +4208,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D150" s="1">
-        <v>646.50000000000023</v>
+        <v>610.6666666666672</v>
       </c>
       <c r="E150" s="2">
-        <v>0.98828025477707271</v>
+        <v>0.98733495014821093</v>
       </c>
       <c r="F150" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>183</v>
+        <v>151</v>
       </c>
       <c r="B151">
         <v>1</v>
@@ -4228,13 +4228,13 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D151" s="1">
-        <v>646.66666666666686</v>
+        <v>610.83333333333383</v>
       </c>
       <c r="E151" s="2">
-        <v>0.98853503184713631</v>
+        <v>0.98760441929399367</v>
       </c>
       <c r="F151" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
@@ -4248,18 +4248,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D152" s="1">
-        <v>646.83333333333348</v>
+        <v>611.00000000000045</v>
       </c>
       <c r="E152" s="2">
-        <v>0.98878980891720003</v>
+        <v>0.98787388843977642</v>
       </c>
       <c r="F152" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B153">
         <v>1</v>
@@ -4268,18 +4268,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D153" s="1">
-        <v>647.00000000000011</v>
+        <v>611.16666666666708</v>
       </c>
       <c r="E153" s="2">
-        <v>0.98904458598726364</v>
+        <v>0.98814335758555916</v>
       </c>
       <c r="F153" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -4288,18 +4288,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D154" s="1">
-        <v>647.16666666666674</v>
+        <v>611.33333333333371</v>
       </c>
       <c r="E154" s="2">
-        <v>0.98929936305732724</v>
+        <v>0.9884128267313419</v>
       </c>
       <c r="F154" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -4308,18 +4308,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D155" s="1">
-        <v>647.33333333333337</v>
+        <v>611.50000000000034</v>
       </c>
       <c r="E155" s="2">
-        <v>0.98955414012739085</v>
+        <v>0.98868229587712464</v>
       </c>
       <c r="F155" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>187</v>
+        <v>218</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -4328,18 +4328,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D156" s="1">
-        <v>647.5</v>
+        <v>611.66666666666697</v>
       </c>
       <c r="E156" s="2">
-        <v>0.98980891719745456</v>
+        <v>0.98895176502290738</v>
       </c>
       <c r="F156" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>188</v>
+        <v>165</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -4348,18 +4348,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D157" s="1">
-        <v>647.66666666666663</v>
+        <v>611.8333333333336</v>
       </c>
       <c r="E157" s="2">
-        <v>0.99006369426751817</v>
+        <v>0.98922123416869012</v>
       </c>
       <c r="F157" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A158" s="3">
-        <v>9410912000</v>
+      <c r="A158" s="3" t="s">
+        <v>171</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -4368,18 +4368,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D158" s="1">
-        <v>647.83333333333326</v>
+        <v>612.00000000000023</v>
       </c>
       <c r="E158" s="2">
-        <v>0.99031847133758177</v>
+        <v>0.98949070331447286</v>
       </c>
       <c r="F158" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>57</v>
+        <v>157</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -4388,18 +4388,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D159" s="1">
-        <v>647.99999999999989</v>
+        <v>612.16666666666686</v>
       </c>
       <c r="E159" s="2">
-        <v>0.99057324840764538</v>
+        <v>0.98976017246025561</v>
       </c>
       <c r="F159" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>189</v>
+        <v>68</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -4408,18 +4408,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D160" s="1">
-        <v>648.16666666666652</v>
+        <v>612.33333333333348</v>
       </c>
       <c r="E160" s="2">
-        <v>0.9908280254777091</v>
+        <v>0.99002964160603835</v>
       </c>
       <c r="F160" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>190</v>
+        <v>64</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -4428,18 +4428,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D161" s="1">
-        <v>648.33333333333314</v>
+        <v>612.50000000000011</v>
       </c>
       <c r="E161" s="2">
-        <v>0.9910828025477727</v>
+        <v>0.99029911075182109</v>
       </c>
       <c r="F161" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>191</v>
+        <v>43</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -4448,18 +4448,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D162" s="1">
-        <v>648.49999999999977</v>
+        <v>612.66666666666674</v>
       </c>
       <c r="E162" s="2">
-        <v>0.99133757961783631</v>
+        <v>0.99056857989760383</v>
       </c>
       <c r="F162" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -4468,18 +4468,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D163" s="1">
-        <v>648.6666666666664</v>
+        <v>612.83333333333337</v>
       </c>
       <c r="E163" s="2">
-        <v>0.99159235668790002</v>
+        <v>0.99083804904338657</v>
       </c>
       <c r="F163" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -4488,18 +4488,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D164" s="1">
-        <v>648.83333333333303</v>
+        <v>613</v>
       </c>
       <c r="E164" s="2">
-        <v>0.99184713375796363</v>
+        <v>0.99110751818916931</v>
       </c>
       <c r="F164" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>58</v>
+        <v>158</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -4508,18 +4508,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D165" s="1">
-        <v>648.99999999999966</v>
+        <v>613.16666666666663</v>
       </c>
       <c r="E165" s="2">
-        <v>0.99210191082802723</v>
+        <v>0.99137698733495205</v>
       </c>
       <c r="F165" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -4528,18 +4528,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D166" s="1">
-        <v>649.16666666666629</v>
+        <v>613.33333333333326</v>
       </c>
       <c r="E166" s="2">
-        <v>0.99235668789809084</v>
+        <v>0.99164645648073479</v>
       </c>
       <c r="F166" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -4548,18 +4548,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D167" s="1">
-        <v>649.33333333333292</v>
+        <v>613.49999999999989</v>
       </c>
       <c r="E167" s="2">
-        <v>0.99261146496815456</v>
+        <v>0.99191592562651754</v>
       </c>
       <c r="F167" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -4568,18 +4568,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D168" s="1">
-        <v>649.49999999999955</v>
+        <v>613.66666666666652</v>
       </c>
       <c r="E168" s="2">
-        <v>0.99286624203821816</v>
+        <v>0.99218539477230028</v>
       </c>
       <c r="F168" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>197</v>
+        <v>221</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -4588,18 +4588,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D169" s="1">
-        <v>649.66666666666617</v>
+        <v>613.83333333333314</v>
       </c>
       <c r="E169" s="2">
-        <v>0.99312101910828177</v>
+        <v>0.99245486391808313</v>
       </c>
       <c r="F169" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>43</v>
+        <v>184</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -4608,18 +4608,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D170" s="1">
-        <v>649.8333333333328</v>
+        <v>613.99999999999977</v>
       </c>
       <c r="E170" s="2">
-        <v>0.99337579617834548</v>
+        <v>0.99272433306386587</v>
       </c>
       <c r="F170" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>198</v>
+        <v>177</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -4628,18 +4628,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D171" s="1">
-        <v>649.99999999999943</v>
+        <v>614.1666666666664</v>
       </c>
       <c r="E171" s="2">
-        <v>0.99363057324840909</v>
+        <v>0.99299380220964861</v>
       </c>
       <c r="F171" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>53</v>
+        <v>167</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -4648,18 +4648,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D172" s="1">
-        <v>650.16666666666606</v>
+        <v>614.33333333333303</v>
       </c>
       <c r="E172" s="2">
-        <v>0.99388535031847269</v>
+        <v>0.99326327135543135</v>
       </c>
       <c r="F172" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -4668,18 +4668,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D173" s="1">
-        <v>650.33333333333269</v>
+        <v>614.49999999999966</v>
       </c>
       <c r="E173" s="2">
-        <v>0.9941401273885363</v>
+        <v>0.9935327405012141</v>
       </c>
       <c r="F173" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>200</v>
+        <v>156</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -4688,18 +4688,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D174" s="1">
-        <v>650.49999999999932</v>
+        <v>614.66666666666629</v>
       </c>
       <c r="E174" s="2">
-        <v>0.99439490445860002</v>
+        <v>0.99380220964699684</v>
       </c>
       <c r="F174" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -4708,18 +4708,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D175" s="1">
-        <v>650.66666666666595</v>
+        <v>614.83333333333292</v>
       </c>
       <c r="E175" s="2">
-        <v>0.99464968152866362</v>
+        <v>0.99407167879277958</v>
       </c>
       <c r="F175" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>202</v>
+        <v>222</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -4728,18 +4728,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D176" s="1">
-        <v>650.83333333333258</v>
+        <v>614.99999999999955</v>
       </c>
       <c r="E176" s="2">
-        <v>0.99490445859872723</v>
+        <v>0.99434114793856232</v>
       </c>
       <c r="F176" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>203</v>
+        <v>48</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -4748,18 +4748,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D177" s="1">
-        <v>650.9999999999992</v>
+        <v>615.16666666666617</v>
       </c>
       <c r="E177" s="2">
-        <v>0.99515923566879094</v>
+        <v>0.99461061708434506</v>
       </c>
       <c r="F177" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>204</v>
+        <v>190</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -4768,18 +4768,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D178" s="1">
-        <v>651.16666666666583</v>
+        <v>615.3333333333328</v>
       </c>
       <c r="E178" s="2">
-        <v>0.99541401273885455</v>
+        <v>0.9948800862301278</v>
       </c>
       <c r="F178" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -4788,18 +4788,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D179" s="1">
-        <v>651.33333333333246</v>
+        <v>615.49999999999943</v>
       </c>
       <c r="E179" s="2">
-        <v>0.99566878980891815</v>
+        <v>0.99514955537591054</v>
       </c>
       <c r="F179" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -4808,18 +4808,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D180" s="1">
-        <v>651.49999999999909</v>
+        <v>615.66666666666606</v>
       </c>
       <c r="E180" s="2">
-        <v>0.99592356687898176</v>
+        <v>0.99541902452169329</v>
       </c>
       <c r="F180" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>207</v>
+        <v>175</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -4828,18 +4828,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D181" s="1">
-        <v>651.66666666666572</v>
+        <v>615.83333333333269</v>
       </c>
       <c r="E181" s="2">
-        <v>0.99617834394904548</v>
+        <v>0.99568849366747603</v>
       </c>
       <c r="F181" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>208</v>
+        <v>141</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -4848,18 +4848,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D182" s="1">
-        <v>651.83333333333235</v>
+        <v>615.99999999999932</v>
       </c>
       <c r="E182" s="2">
-        <v>0.99643312101910908</v>
+        <v>0.99595796281325877</v>
       </c>
       <c r="F182" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>209</v>
+        <v>53</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -4868,18 +4868,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D183" s="1">
-        <v>651.99999999999898</v>
+        <v>616.16666666666595</v>
       </c>
       <c r="E183" s="2">
-        <v>0.99668789808917269</v>
+        <v>0.99622743195904151</v>
       </c>
       <c r="F183" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -4888,18 +4888,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D184" s="1">
-        <v>652.16666666666561</v>
+        <v>616.33333333333258</v>
       </c>
       <c r="E184" s="2">
-        <v>0.9969426751592364</v>
+        <v>0.99649690110482425</v>
       </c>
       <c r="F184" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>211</v>
+        <v>225</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -4908,18 +4908,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D185" s="1">
-        <v>652.33333333333223</v>
+        <v>616.4999999999992</v>
       </c>
       <c r="E185" s="2">
-        <v>0.99719745222930001</v>
+        <v>0.99676637025060699</v>
       </c>
       <c r="F185" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>212</v>
+        <v>153</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -4928,18 +4928,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D186" s="1">
-        <v>652.49999999999886</v>
+        <v>616.66666666666583</v>
       </c>
       <c r="E186" s="2">
-        <v>0.99745222929936361</v>
+        <v>0.99703583939638973</v>
       </c>
       <c r="F186" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>66</v>
+        <v>226</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -4948,18 +4948,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D187" s="1">
-        <v>652.66666666666549</v>
+        <v>616.83333333333246</v>
       </c>
       <c r="E187" s="2">
-        <v>0.99770700636942722</v>
+        <v>0.99730530854217248</v>
       </c>
       <c r="F187" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>213</v>
+        <v>159</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -4968,18 +4968,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D188" s="1">
-        <v>652.83333333333212</v>
+        <v>616.99999999999909</v>
       </c>
       <c r="E188" s="2">
-        <v>0.99796178343949093</v>
+        <v>0.99757477768795533</v>
       </c>
       <c r="F188" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>214</v>
+        <v>178</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -4988,18 +4988,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D189" s="1">
-        <v>652.99999999999875</v>
+        <v>617.16666666666572</v>
       </c>
       <c r="E189" s="2">
-        <v>0.99821656050955454</v>
+        <v>0.99784424683373807</v>
       </c>
       <c r="F189" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>62</v>
+        <v>227</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -5008,18 +5008,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D190" s="1">
-        <v>653.16666666666538</v>
+        <v>617.33333333333235</v>
       </c>
       <c r="E190" s="2">
-        <v>0.99847133757961815</v>
+        <v>0.99811371597952081</v>
       </c>
       <c r="F190" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>215</v>
+        <v>63</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -5028,18 +5028,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D191" s="1">
-        <v>653.33333333333201</v>
+        <v>617.49999999999898</v>
       </c>
       <c r="E191" s="2">
-        <v>0.99872611464968186</v>
+        <v>0.99838318512530355</v>
       </c>
       <c r="F191" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -5048,18 +5048,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D192" s="1">
-        <v>653.49999999999864</v>
+        <v>617.66666666666561</v>
       </c>
       <c r="E192" s="2">
-        <v>0.99898089171974547</v>
+        <v>0.99865265427108629</v>
       </c>
       <c r="F192" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
-        <v>216</v>
+        <v>179</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -5068,18 +5068,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D193" s="1">
-        <v>653.66666666666526</v>
+        <v>617.83333333333223</v>
       </c>
       <c r="E193" s="2">
-        <v>0.99923566878980907</v>
+        <v>0.99892212341686903</v>
       </c>
       <c r="F193" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
-        <v>217</v>
+        <v>189</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -5088,18 +5088,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D194" s="1">
-        <v>653.83333333333189</v>
+        <v>617.99999999999886</v>
       </c>
       <c r="E194" s="2">
-        <v>0.99949044585987268</v>
+        <v>0.99919159256265178</v>
       </c>
       <c r="F194" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="3" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -5108,18 +5108,18 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D195" s="1">
-        <v>653.99999999999852</v>
+        <v>618.16666666666549</v>
       </c>
       <c r="E195" s="2">
-        <v>0.99974522292993639</v>
+        <v>0.99946106170843452</v>
       </c>
       <c r="F195" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -5128,13 +5128,33 @@
         <v>0.16666666666666666</v>
       </c>
       <c r="D196" s="1">
-        <v>654.16666666666515</v>
+        <v>618.33333333333212</v>
       </c>
       <c r="E196" s="2">
-        <v>1</v>
+        <v>0.99973053085421726</v>
       </c>
       <c r="F196" t="s">
-        <v>75</v>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A197" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B197">
+        <v>1</v>
+      </c>
+      <c r="C197" s="1">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="D197" s="1">
+        <v>618.49999999999875</v>
+      </c>
+      <c r="E197" s="2">
+        <v>1</v>
+      </c>
+      <c r="F197" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -5147,7 +5167,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{80827961-A801-4B86-A12E-303011668596}">
-  <dimension ref="A1:C238"/>
+  <dimension ref="A1:C235"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.5703125" style="3" bestFit="1" customWidth="1"/>
@@ -5157,57 +5177,57 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B1" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="C1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B2">
-        <v>3291</v>
+        <v>3375</v>
       </c>
       <c r="C2">
-        <v>549</v>
+        <v>563</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="B3">
-        <v>2337</v>
+        <v>2081</v>
       </c>
       <c r="C3">
-        <v>390</v>
+        <v>347</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B4">
-        <v>794</v>
+        <v>800</v>
       </c>
       <c r="C4">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>220</v>
+        <v>80</v>
       </c>
       <c r="B5">
-        <v>623</v>
+        <v>665</v>
       </c>
       <c r="C5">
-        <v>104</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -5215,43 +5235,43 @@
         <v>83</v>
       </c>
       <c r="B6">
-        <v>521</v>
+        <v>437</v>
       </c>
       <c r="C6">
-        <v>87</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="B7">
-        <v>493</v>
+        <v>402</v>
       </c>
       <c r="C7">
-        <v>83</v>
+        <v>67</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>99</v>
+        <v>199</v>
       </c>
       <c r="B8">
-        <v>468</v>
+        <v>383</v>
       </c>
       <c r="C8">
-        <v>78</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B9">
-        <v>259</v>
+        <v>246</v>
       </c>
       <c r="C9">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.25">
@@ -5259,10 +5279,10 @@
         <v>12</v>
       </c>
       <c r="B10">
-        <v>230</v>
+        <v>212</v>
       </c>
       <c r="C10">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.25">
@@ -5270,73 +5290,73 @@
         <v>7</v>
       </c>
       <c r="B11">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c r="C11">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>8</v>
+        <v>200</v>
       </c>
       <c r="B12">
-        <v>183</v>
+        <v>209</v>
       </c>
       <c r="C12">
-        <v>31</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>221</v>
+        <v>8</v>
       </c>
       <c r="B13">
-        <v>164</v>
+        <v>185</v>
       </c>
       <c r="C13">
-        <v>28</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="B14">
-        <v>156</v>
+        <v>170</v>
       </c>
       <c r="C14">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B15">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C15">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="C16">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>87</v>
+        <v>6</v>
       </c>
       <c r="B17">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C17">
         <v>21</v>
@@ -5344,13 +5364,13 @@
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B18">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C18">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
@@ -5358,18 +5378,18 @@
         <v>16</v>
       </c>
       <c r="B19">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C19">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
       <c r="B20">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="C20">
         <v>17</v>
@@ -5377,10 +5397,10 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="B21">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C21">
         <v>16</v>
@@ -5391,7 +5411,7 @@
         <v>88</v>
       </c>
       <c r="B22">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C22">
         <v>15</v>
@@ -5399,40 +5419,40 @@
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>33</v>
+        <v>85</v>
       </c>
       <c r="B23">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="C23">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="B24">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="C24">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B25">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C25">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="B26">
         <v>71</v>
@@ -5443,7 +5463,7 @@
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B27">
         <v>70</v>
@@ -5454,153 +5474,153 @@
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B28">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C28">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>91</v>
+        <v>10</v>
       </c>
       <c r="B29">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C29">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B30">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="C30">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="B31">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C31">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>89</v>
+        <v>27</v>
       </c>
       <c r="B32">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C32">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>104</v>
+        <v>28</v>
       </c>
       <c r="B33">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C33">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="B34">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="C34">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="B35">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="C35">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>9</v>
+        <v>44</v>
       </c>
       <c r="B36">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C36">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>47</v>
+        <v>17</v>
       </c>
       <c r="B37">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="C37">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="B38">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C38">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="B39">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C39">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>105</v>
+        <v>47</v>
       </c>
       <c r="B40">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C40">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="B41">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C41">
         <v>6</v>
@@ -5608,32 +5628,32 @@
     </row>
     <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>107</v>
+        <v>86</v>
       </c>
       <c r="B42">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C42">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="B43">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C43">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>18</v>
+        <v>87</v>
       </c>
       <c r="B44">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C44">
         <v>5</v>
@@ -5641,10 +5661,10 @@
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="B45">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C45">
         <v>5</v>
@@ -5652,7 +5672,7 @@
     </row>
     <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>108</v>
+        <v>14</v>
       </c>
       <c r="B46">
         <v>28</v>
@@ -5663,10 +5683,10 @@
     </row>
     <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>76</v>
+        <v>20</v>
       </c>
       <c r="B47">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C47">
         <v>5</v>
@@ -5674,10 +5694,10 @@
     </row>
     <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="B48">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C48">
         <v>5</v>
@@ -5685,10 +5705,10 @@
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B49">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C49">
         <v>5</v>
@@ -5696,13 +5716,13 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="B50">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C50">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -5710,7 +5730,7 @@
         <v>21</v>
       </c>
       <c r="B51">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C51">
         <v>4</v>
@@ -5718,10 +5738,10 @@
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>109</v>
+        <v>24</v>
       </c>
       <c r="B52">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C52">
         <v>4</v>
@@ -5729,10 +5749,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B53">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C53">
         <v>4</v>
@@ -5740,7 +5760,7 @@
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="B54">
         <v>21</v>
@@ -5751,10 +5771,10 @@
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="B55">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C55">
         <v>4</v>
@@ -5762,29 +5782,29 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>19</v>
+        <v>124</v>
       </c>
       <c r="B56">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C56">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
       <c r="B57">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C57">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
       <c r="B58">
         <v>18</v>
@@ -5795,10 +5815,10 @@
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>112</v>
+        <v>54</v>
       </c>
       <c r="B59">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C59">
         <v>3</v>
@@ -5806,10 +5826,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>111</v>
+        <v>45</v>
       </c>
       <c r="B60">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C60">
         <v>3</v>
@@ -5817,10 +5837,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>61</v>
+        <v>106</v>
       </c>
       <c r="B61">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C61">
         <v>3</v>
@@ -5828,43 +5848,43 @@
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>113</v>
+        <v>41</v>
       </c>
       <c r="B62">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C62">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>114</v>
+        <v>32</v>
       </c>
       <c r="B63">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C63">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>52</v>
+        <v>133</v>
       </c>
       <c r="B64">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C64">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>116</v>
+        <v>19</v>
       </c>
       <c r="B65">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C65">
         <v>2</v>
@@ -5872,10 +5892,10 @@
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>115</v>
+        <v>40</v>
       </c>
       <c r="B66">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C66">
         <v>2</v>
@@ -5883,7 +5903,7 @@
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>118</v>
+        <v>46</v>
       </c>
       <c r="B67">
         <v>11</v>
@@ -5894,7 +5914,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="B68">
         <v>11</v>
@@ -5905,7 +5925,7 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>119</v>
+        <v>67</v>
       </c>
       <c r="B69">
         <v>11</v>
@@ -5916,7 +5936,7 @@
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>40</v>
+        <v>127</v>
       </c>
       <c r="B70">
         <v>10</v>
@@ -5927,7 +5947,7 @@
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>46</v>
+        <v>122</v>
       </c>
       <c r="B71">
         <v>10</v>
@@ -5938,7 +5958,7 @@
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>32</v>
+        <v>126</v>
       </c>
       <c r="B72">
         <v>10</v>
@@ -5949,7 +5969,7 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="B73">
         <v>10</v>
@@ -5960,7 +5980,7 @@
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>63</v>
+        <v>109</v>
       </c>
       <c r="B74">
         <v>9</v>
@@ -5971,7 +5991,7 @@
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>41</v>
+        <v>116</v>
       </c>
       <c r="B75">
         <v>9</v>
@@ -5982,10 +6002,10 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="B76">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C76">
         <v>2</v>
@@ -5993,7 +6013,7 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>120</v>
+        <v>52</v>
       </c>
       <c r="B77">
         <v>8</v>
@@ -6004,7 +6024,7 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>121</v>
+        <v>61</v>
       </c>
       <c r="B78">
         <v>8</v>
@@ -6015,10 +6035,10 @@
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>79</v>
+        <v>162</v>
       </c>
       <c r="B79">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C79">
         <v>2</v>
@@ -6026,7 +6046,7 @@
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B80">
         <v>7</v>
@@ -6037,7 +6057,7 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>30</v>
+        <v>117</v>
       </c>
       <c r="B81">
         <v>7</v>
@@ -6048,29 +6068,29 @@
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="B82">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C82">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="B83">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C83">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>126</v>
+        <v>22</v>
       </c>
       <c r="B84">
         <v>6</v>
@@ -6081,7 +6101,7 @@
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B85">
         <v>6</v>
@@ -6092,7 +6112,7 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>129</v>
+        <v>111</v>
       </c>
       <c r="B86">
         <v>6</v>
@@ -6103,7 +6123,7 @@
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>128</v>
+        <v>76</v>
       </c>
       <c r="B87">
         <v>6</v>
@@ -6114,7 +6134,7 @@
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>127</v>
+        <v>30</v>
       </c>
       <c r="B88">
         <v>6</v>
@@ -6125,10 +6145,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>77</v>
+        <v>207</v>
       </c>
       <c r="B89">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C89">
         <v>1</v>
@@ -6136,7 +6156,7 @@
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>97</v>
+        <v>55</v>
       </c>
       <c r="B90">
         <v>5</v>
@@ -6147,7 +6167,7 @@
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>42</v>
+        <v>92</v>
       </c>
       <c r="B91">
         <v>5</v>
@@ -6158,7 +6178,7 @@
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>222</v>
+        <v>114</v>
       </c>
       <c r="B92">
         <v>5</v>
@@ -6169,7 +6189,7 @@
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>72</v>
+        <v>231</v>
       </c>
       <c r="B93">
         <v>5</v>
@@ -6180,7 +6200,7 @@
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>223</v>
+        <v>134</v>
       </c>
       <c r="B94">
         <v>5</v>
@@ -6191,7 +6211,7 @@
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>132</v>
+        <v>115</v>
       </c>
       <c r="B95">
         <v>5</v>
@@ -6202,10 +6222,10 @@
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>50</v>
+        <v>201</v>
       </c>
       <c r="B96">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C96">
         <v>1</v>
@@ -6213,10 +6233,10 @@
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>133</v>
+        <v>42</v>
       </c>
       <c r="B97">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C97">
         <v>1</v>
@@ -6224,10 +6244,10 @@
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>60</v>
+        <v>121</v>
       </c>
       <c r="B98">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C98">
         <v>1</v>
@@ -6235,10 +6255,10 @@
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="B99">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C99">
         <v>1</v>
@@ -6246,10 +6266,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>55</v>
+        <v>135</v>
       </c>
       <c r="B100">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C100">
         <v>1</v>
@@ -6257,10 +6277,10 @@
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B101">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C101">
         <v>1</v>
@@ -6268,10 +6288,10 @@
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" s="3" t="s">
-        <v>134</v>
+        <v>39</v>
       </c>
       <c r="B102">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C102">
         <v>1</v>
@@ -6279,10 +6299,10 @@
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" s="3" t="s">
-        <v>135</v>
+        <v>58</v>
       </c>
       <c r="B103">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C103">
         <v>1</v>
@@ -6290,10 +6310,10 @@
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A104" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B104">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C104">
         <v>1</v>
@@ -6301,10 +6321,10 @@
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A105" s="3" t="s">
-        <v>139</v>
+        <v>130</v>
       </c>
       <c r="B105">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C105">
         <v>1</v>
@@ -6312,10 +6332,10 @@
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A106" s="3" t="s">
-        <v>138</v>
+        <v>50</v>
       </c>
       <c r="B106">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C106">
         <v>1</v>
@@ -6323,10 +6343,10 @@
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A107" s="3" t="s">
-        <v>92</v>
+        <v>147</v>
       </c>
       <c r="B107">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C107">
         <v>1</v>
@@ -6334,10 +6354,10 @@
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A108" s="3" t="s">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="B108">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C108">
         <v>1</v>
@@ -6345,10 +6365,10 @@
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A109" s="3" t="s">
-        <v>34</v>
+        <v>108</v>
       </c>
       <c r="B109">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C109">
         <v>1</v>
@@ -6356,18 +6376,18 @@
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A110" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B110">
+        <v>3</v>
+      </c>
+      <c r="C110">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A111" s="3" t="s">
         <v>136</v>
-      </c>
-      <c r="B110">
-        <v>4</v>
-      </c>
-      <c r="C110">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A111" s="3">
-        <v>91351642000</v>
       </c>
       <c r="B111">
         <v>3</v>
@@ -6378,7 +6398,7 @@
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A112" s="3" t="s">
-        <v>67</v>
+        <v>128</v>
       </c>
       <c r="B112">
         <v>3</v>
@@ -6389,10 +6409,10 @@
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A113" s="3" t="s">
-        <v>141</v>
+        <v>233</v>
       </c>
       <c r="B113">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C113">
         <v>1</v>
@@ -6400,10 +6420,10 @@
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" s="3" t="s">
-        <v>39</v>
+        <v>234</v>
       </c>
       <c r="B114">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C114">
         <v>1</v>
@@ -6411,10 +6431,10 @@
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A115" s="3" t="s">
-        <v>145</v>
+        <v>66</v>
       </c>
       <c r="B115">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C115">
         <v>1</v>
@@ -6422,10 +6442,10 @@
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A116" s="3" t="s">
-        <v>143</v>
+        <v>31</v>
       </c>
       <c r="B116">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C116">
         <v>1</v>
@@ -6433,10 +6453,10 @@
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A117" s="3" t="s">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="B117">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C117">
         <v>1</v>
@@ -6444,10 +6464,10 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118" s="3" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B118">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C118">
         <v>1</v>
@@ -6455,10 +6475,10 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" s="3" t="s">
-        <v>142</v>
+        <v>187</v>
       </c>
       <c r="B119">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C119">
         <v>1</v>
@@ -6466,10 +6486,10 @@
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" s="3" t="s">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="B120">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C120">
         <v>1</v>
@@ -6477,7 +6497,7 @@
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" s="3" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="B121">
         <v>2</v>
@@ -6488,7 +6508,7 @@
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="B122">
         <v>2</v>
@@ -6499,7 +6519,7 @@
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A123" s="3" t="s">
-        <v>155</v>
+        <v>180</v>
       </c>
       <c r="B123">
         <v>2</v>
@@ -6510,7 +6530,7 @@
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A124" s="3" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B124">
         <v>2</v>
@@ -6521,7 +6541,7 @@
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A125" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="B125">
         <v>2</v>
@@ -6532,7 +6552,7 @@
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A126" s="3" t="s">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="B126">
         <v>2</v>
@@ -6543,7 +6563,7 @@
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A127" s="3" t="s">
-        <v>152</v>
+        <v>70</v>
       </c>
       <c r="B127">
         <v>2</v>
@@ -6554,7 +6574,7 @@
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A128" s="3" t="s">
-        <v>64</v>
+        <v>235</v>
       </c>
       <c r="B128">
         <v>2</v>
@@ -6565,7 +6585,7 @@
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A129" s="3" t="s">
-        <v>156</v>
+        <v>34</v>
       </c>
       <c r="B129">
         <v>2</v>
@@ -6576,7 +6596,7 @@
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A130" s="3" t="s">
-        <v>48</v>
+        <v>150</v>
       </c>
       <c r="B130">
         <v>2</v>
@@ -6586,8 +6606,8 @@
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A131" s="3">
-        <v>9805657723</v>
+      <c r="A131" s="3" t="s">
+        <v>138</v>
       </c>
       <c r="B131">
         <v>2</v>
@@ -6598,7 +6618,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A132" s="3" t="s">
-        <v>157</v>
+        <v>210</v>
       </c>
       <c r="B132">
         <v>2</v>
@@ -6609,7 +6629,7 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A133" s="3" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="B133">
         <v>2</v>
@@ -6620,7 +6640,7 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" s="3" t="s">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="B134">
         <v>2</v>
@@ -6631,7 +6651,7 @@
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A135" s="3" t="s">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="B135">
         <v>2</v>
@@ -6642,7 +6662,7 @@
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A136" s="3" t="s">
-        <v>74</v>
+        <v>176</v>
       </c>
       <c r="B136">
         <v>2</v>
@@ -6653,7 +6673,7 @@
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A137" s="3" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="B137">
         <v>2</v>
@@ -6664,7 +6684,7 @@
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A138" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="B138">
         <v>2</v>
@@ -6675,7 +6695,7 @@
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A139" s="3" t="s">
-        <v>59</v>
+        <v>166</v>
       </c>
       <c r="B139">
         <v>2</v>
@@ -6686,7 +6706,7 @@
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A140" s="3" t="s">
-        <v>225</v>
+        <v>37</v>
       </c>
       <c r="B140">
         <v>2</v>
@@ -6697,7 +6717,7 @@
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A141" s="3" t="s">
-        <v>158</v>
+        <v>90</v>
       </c>
       <c r="B141">
         <v>2</v>
@@ -6708,7 +6728,7 @@
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A142" s="3" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="B142">
         <v>2</v>
@@ -6719,7 +6739,7 @@
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A143" s="3" t="s">
-        <v>37</v>
+        <v>149</v>
       </c>
       <c r="B143">
         <v>2</v>
@@ -6730,10 +6750,10 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" s="3" t="s">
-        <v>215</v>
+        <v>169</v>
       </c>
       <c r="B144">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C144">
         <v>1</v>
@@ -6741,10 +6761,10 @@
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A145" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B145">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C145">
         <v>1</v>
@@ -6752,10 +6772,10 @@
     </row>
     <row r="146" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A146" s="3" t="s">
-        <v>226</v>
+        <v>146</v>
       </c>
       <c r="B146">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C146">
         <v>1</v>
@@ -6763,10 +6783,10 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" s="3" t="s">
-        <v>66</v>
+        <v>152</v>
       </c>
       <c r="B147">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C147">
         <v>1</v>
@@ -6777,7 +6797,7 @@
         <v>208</v>
       </c>
       <c r="B148">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C148">
         <v>1</v>
@@ -6785,10 +6805,10 @@
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A149" s="3" t="s">
-        <v>174</v>
+        <v>209</v>
       </c>
       <c r="B149">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C149">
         <v>1</v>
@@ -6796,10 +6816,10 @@
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" s="3" t="s">
-        <v>198</v>
+        <v>168</v>
       </c>
       <c r="B150">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C150">
         <v>1</v>
@@ -6807,10 +6827,10 @@
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A151" s="3" t="s">
-        <v>207</v>
+        <v>236</v>
       </c>
       <c r="B151">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C151">
         <v>1</v>
@@ -6818,10 +6838,10 @@
     </row>
     <row r="152" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A152" s="3" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="B152">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C152">
         <v>1</v>
@@ -6829,10 +6849,10 @@
     </row>
     <row r="153" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A153" s="3" t="s">
-        <v>176</v>
+        <v>143</v>
       </c>
       <c r="B153">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C153">
         <v>1</v>
@@ -6840,7 +6860,7 @@
     </row>
     <row r="154" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A154" s="3" t="s">
-        <v>166</v>
+        <v>197</v>
       </c>
       <c r="B154">
         <v>1</v>
@@ -6851,7 +6871,7 @@
     </row>
     <row r="155" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A155" s="3" t="s">
-        <v>212</v>
+        <v>238</v>
       </c>
       <c r="B155">
         <v>1</v>
@@ -6862,7 +6882,7 @@
     </row>
     <row r="156" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A156" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="B156">
         <v>1</v>
@@ -6873,7 +6893,7 @@
     </row>
     <row r="157" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A157" s="3" t="s">
-        <v>49</v>
+        <v>183</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -6884,7 +6904,7 @@
     </row>
     <row r="158" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A158" s="3" t="s">
-        <v>165</v>
+        <v>68</v>
       </c>
       <c r="B158">
         <v>1</v>
@@ -6895,7 +6915,7 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" s="3" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="B159">
         <v>1</v>
@@ -6906,7 +6926,7 @@
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A160" s="3" t="s">
-        <v>229</v>
+        <v>165</v>
       </c>
       <c r="B160">
         <v>1</v>
@@ -6917,7 +6937,7 @@
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A161" s="3" t="s">
-        <v>62</v>
+        <v>225</v>
       </c>
       <c r="B161">
         <v>1</v>
@@ -6928,7 +6948,7 @@
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" s="3" t="s">
-        <v>230</v>
+        <v>171</v>
       </c>
       <c r="B162">
         <v>1</v>
@@ -6939,7 +6959,7 @@
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A163" s="3" t="s">
-        <v>56</v>
+        <v>191</v>
       </c>
       <c r="B163">
         <v>1</v>
@@ -6950,7 +6970,7 @@
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A164" s="3" t="s">
-        <v>95</v>
+        <v>202</v>
       </c>
       <c r="B164">
         <v>1</v>
@@ -6961,7 +6981,7 @@
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A165" s="3" t="s">
-        <v>210</v>
+        <v>71</v>
       </c>
       <c r="B165">
         <v>1</v>
@@ -6972,7 +6992,7 @@
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A166" s="3" t="s">
-        <v>182</v>
+        <v>60</v>
       </c>
       <c r="B166">
         <v>1</v>
@@ -6983,7 +7003,7 @@
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A167" s="3" t="s">
-        <v>57</v>
+        <v>230</v>
       </c>
       <c r="B167">
         <v>1</v>
@@ -6994,7 +7014,7 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" s="3" t="s">
-        <v>206</v>
+        <v>240</v>
       </c>
       <c r="B168">
         <v>1</v>
@@ -7005,7 +7025,7 @@
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A169" s="3" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="B169">
         <v>1</v>
@@ -7016,7 +7036,7 @@
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A170" s="3" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="B170">
         <v>1</v>
@@ -7027,7 +7047,7 @@
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A171" s="3" t="s">
-        <v>192</v>
+        <v>226</v>
       </c>
       <c r="B171">
         <v>1</v>
@@ -7038,7 +7058,7 @@
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A172" s="3" t="s">
-        <v>231</v>
+        <v>188</v>
       </c>
       <c r="B172">
         <v>1</v>
@@ -7049,7 +7069,7 @@
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A173" s="3" t="s">
-        <v>58</v>
+        <v>219</v>
       </c>
       <c r="B173">
         <v>1</v>
@@ -7060,7 +7080,7 @@
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A174" s="3" t="s">
-        <v>71</v>
+        <v>161</v>
       </c>
       <c r="B174">
         <v>1</v>
@@ -7071,7 +7091,7 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" s="3" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="B175">
         <v>1</v>
@@ -7082,7 +7102,7 @@
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A176" s="3" t="s">
-        <v>193</v>
+        <v>229</v>
       </c>
       <c r="B176">
         <v>1</v>
@@ -7093,7 +7113,7 @@
     </row>
     <row r="177" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A177" s="3" t="s">
-        <v>195</v>
+        <v>177</v>
       </c>
       <c r="B177">
         <v>1</v>
@@ -7104,7 +7124,7 @@
     </row>
     <row r="178" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A178" s="3" t="s">
-        <v>232</v>
+        <v>193</v>
       </c>
       <c r="B178">
         <v>1</v>
@@ -7115,7 +7135,7 @@
     </row>
     <row r="179" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A179" s="3" t="s">
-        <v>216</v>
+        <v>48</v>
       </c>
       <c r="B179">
         <v>1</v>
@@ -7126,7 +7146,7 @@
     </row>
     <row r="180" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A180" s="3" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="B180">
         <v>1</v>
@@ -7137,7 +7157,7 @@
     </row>
     <row r="181" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A181" s="3" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="B181">
         <v>1</v>
@@ -7148,7 +7168,7 @@
     </row>
     <row r="182" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A182" s="3" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="B182">
         <v>1</v>
@@ -7159,7 +7179,7 @@
     </row>
     <row r="183" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A183" s="3" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="B183">
         <v>1</v>
@@ -7170,7 +7190,7 @@
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A184" s="3" t="s">
-        <v>234</v>
+        <v>53</v>
       </c>
       <c r="B184">
         <v>1</v>
@@ -7181,7 +7201,7 @@
     </row>
     <row r="185" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A185" s="3" t="s">
-        <v>190</v>
+        <v>173</v>
       </c>
       <c r="B185">
         <v>1</v>
@@ -7192,7 +7212,7 @@
     </row>
     <row r="186" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A186" s="3" t="s">
-        <v>235</v>
+        <v>205</v>
       </c>
       <c r="B186">
         <v>1</v>
@@ -7203,7 +7223,7 @@
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A187" s="3" t="s">
-        <v>173</v>
+        <v>241</v>
       </c>
       <c r="B187">
         <v>1</v>
@@ -7214,7 +7234,7 @@
     </row>
     <row r="188" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A188" s="3" t="s">
-        <v>163</v>
+        <v>57</v>
       </c>
       <c r="B188">
         <v>1</v>
@@ -7225,7 +7245,7 @@
     </row>
     <row r="189" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A189" s="3" t="s">
-        <v>179</v>
+        <v>211</v>
       </c>
       <c r="B189">
         <v>1</v>
@@ -7236,7 +7256,7 @@
     </row>
     <row r="190" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A190" s="3" t="s">
-        <v>202</v>
+        <v>154</v>
       </c>
       <c r="B190">
         <v>1</v>
@@ -7247,7 +7267,7 @@
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A191" s="3" t="s">
-        <v>217</v>
+        <v>178</v>
       </c>
       <c r="B191">
         <v>1</v>
@@ -7258,7 +7278,7 @@
     </row>
     <row r="192" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A192" s="3" t="s">
-        <v>204</v>
+        <v>156</v>
       </c>
       <c r="B192">
         <v>1</v>
@@ -7269,7 +7289,7 @@
     </row>
     <row r="193" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A193" s="3" t="s">
-        <v>205</v>
+        <v>63</v>
       </c>
       <c r="B193">
         <v>1</v>
@@ -7280,7 +7300,7 @@
     </row>
     <row r="194" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A194" s="3" t="s">
-        <v>164</v>
+        <v>222</v>
       </c>
       <c r="B194">
         <v>1</v>
@@ -7290,8 +7310,8 @@
       </c>
     </row>
     <row r="195" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A195" s="3">
-        <v>9410912000</v>
+      <c r="A195" s="3" t="s">
+        <v>242</v>
       </c>
       <c r="B195">
         <v>1</v>
@@ -7302,7 +7322,7 @@
     </row>
     <row r="196" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A196" s="3" t="s">
-        <v>94</v>
+        <v>190</v>
       </c>
       <c r="B196">
         <v>1</v>
@@ -7313,7 +7333,7 @@
     </row>
     <row r="197" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A197" s="3" t="s">
-        <v>211</v>
+        <v>243</v>
       </c>
       <c r="B197">
         <v>1</v>
@@ -7324,7 +7344,7 @@
     </row>
     <row r="198" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A198" s="3" t="s">
-        <v>171</v>
+        <v>223</v>
       </c>
       <c r="B198">
         <v>1</v>
@@ -7335,7 +7355,7 @@
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A199" s="3" t="s">
-        <v>236</v>
+        <v>89</v>
       </c>
       <c r="B199">
         <v>1</v>
@@ -7346,7 +7366,7 @@
     </row>
     <row r="200" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A200" s="3" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B200">
         <v>1</v>
@@ -7357,7 +7377,7 @@
     </row>
     <row r="201" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A201" s="3" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="B201">
         <v>1</v>
@@ -7368,7 +7388,7 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" s="3" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="B202">
         <v>1</v>
@@ -7379,7 +7399,7 @@
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" s="3" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B203">
         <v>1</v>
@@ -7390,7 +7410,7 @@
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A204" s="3" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="B204">
         <v>1</v>
@@ -7401,7 +7421,7 @@
     </row>
     <row r="205" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A205" s="3" t="s">
-        <v>185</v>
+        <v>228</v>
       </c>
       <c r="B205">
         <v>1</v>
@@ -7412,7 +7432,7 @@
     </row>
     <row r="206" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A206" s="3" t="s">
-        <v>209</v>
+        <v>155</v>
       </c>
       <c r="B206">
         <v>1</v>
@@ -7423,7 +7443,7 @@
     </row>
     <row r="207" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A207" s="3" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="B207">
         <v>1</v>
@@ -7434,7 +7454,7 @@
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A208" s="3" t="s">
-        <v>160</v>
+        <v>224</v>
       </c>
       <c r="B208">
         <v>1</v>
@@ -7445,7 +7465,7 @@
     </row>
     <row r="209" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A209" s="3" t="s">
-        <v>175</v>
+        <v>43</v>
       </c>
       <c r="B209">
         <v>1</v>
@@ -7456,7 +7476,7 @@
     </row>
     <row r="210" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A210" s="3" t="s">
-        <v>188</v>
+        <v>153</v>
       </c>
       <c r="B210">
         <v>1</v>
@@ -7467,7 +7487,7 @@
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A211" s="3" t="s">
-        <v>191</v>
+        <v>212</v>
       </c>
       <c r="B211">
         <v>1</v>
@@ -7478,7 +7498,7 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" s="3" t="s">
-        <v>214</v>
+        <v>56</v>
       </c>
       <c r="B212">
         <v>1</v>
@@ -7489,7 +7509,7 @@
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" s="3" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="B213">
         <v>1</v>
@@ -7500,7 +7520,7 @@
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A214" s="3" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="B214">
         <v>1</v>
@@ -7511,7 +7531,7 @@
     </row>
     <row r="215" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A215" s="3" t="s">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="B215">
         <v>1</v>
@@ -7522,7 +7542,7 @@
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" s="3" t="s">
-        <v>238</v>
+        <v>192</v>
       </c>
       <c r="B216">
         <v>1</v>
@@ -7533,7 +7553,7 @@
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" s="3" t="s">
-        <v>199</v>
+        <v>174</v>
       </c>
       <c r="B217">
         <v>1</v>
@@ -7544,7 +7564,7 @@
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A218" s="3" t="s">
-        <v>239</v>
+        <v>93</v>
       </c>
       <c r="B218">
         <v>1</v>
@@ -7555,7 +7575,7 @@
     </row>
     <row r="219" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A219" s="3" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
       <c r="B219">
         <v>1</v>
@@ -7566,7 +7586,7 @@
     </row>
     <row r="220" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A220" s="3" t="s">
-        <v>240</v>
+        <v>203</v>
       </c>
       <c r="B220">
         <v>1</v>
@@ -7577,7 +7597,7 @@
     </row>
     <row r="221" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A221" s="3" t="s">
-        <v>65</v>
+        <v>220</v>
       </c>
       <c r="B221">
         <v>1</v>
@@ -7588,7 +7608,7 @@
     </row>
     <row r="222" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A222" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B222">
         <v>1</v>
@@ -7599,7 +7619,7 @@
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A223" s="3" t="s">
-        <v>203</v>
+        <v>160</v>
       </c>
       <c r="B223">
         <v>1</v>
@@ -7610,7 +7630,7 @@
     </row>
     <row r="224" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A224" s="3" t="s">
-        <v>242</v>
+        <v>204</v>
       </c>
       <c r="B224">
         <v>1</v>
@@ -7621,7 +7641,7 @@
     </row>
     <row r="225" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A225" s="3" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
       <c r="B225">
         <v>1</v>
@@ -7632,7 +7652,7 @@
     </row>
     <row r="226" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A226" s="3" t="s">
-        <v>243</v>
+        <v>158</v>
       </c>
       <c r="B226">
         <v>1</v>
@@ -7643,7 +7663,7 @@
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" s="3" t="s">
-        <v>53</v>
+        <v>213</v>
       </c>
       <c r="B227">
         <v>1</v>
@@ -7654,7 +7674,7 @@
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A228" s="3" t="s">
-        <v>244</v>
+        <v>151</v>
       </c>
       <c r="B228">
         <v>1</v>
@@ -7665,7 +7685,7 @@
     </row>
     <row r="229" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A229" s="3" t="s">
-        <v>43</v>
+        <v>167</v>
       </c>
       <c r="B229">
         <v>1</v>
@@ -7676,7 +7696,7 @@
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A230" s="3" t="s">
-        <v>245</v>
+        <v>217</v>
       </c>
       <c r="B230">
         <v>1</v>
@@ -7687,7 +7707,7 @@
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" s="3" t="s">
-        <v>161</v>
+        <v>186</v>
       </c>
       <c r="B231">
         <v>1</v>
@@ -7698,7 +7718,7 @@
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A232" s="3" t="s">
-        <v>246</v>
+        <v>157</v>
       </c>
       <c r="B232">
         <v>1</v>
@@ -7709,7 +7729,7 @@
     </row>
     <row r="233" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A233" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B233">
         <v>1</v>
@@ -7720,7 +7740,7 @@
     </row>
     <row r="234" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A234" s="3" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="B234">
         <v>1</v>
@@ -7731,45 +7751,12 @@
     </row>
     <row r="235" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A235" s="3" t="s">
-        <v>181</v>
+        <v>64</v>
       </c>
       <c r="B235">
         <v>1</v>
       </c>
       <c r="C235">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A236" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="B236">
-        <v>1</v>
-      </c>
-      <c r="C236">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A237" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="B237">
-        <v>1</v>
-      </c>
-      <c r="C237">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A238" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="B238">
-        <v>1</v>
-      </c>
-      <c r="C238">
         <v>1</v>
       </c>
     </row>
